--- a/Italian_Ratings.xlsx
+++ b/Italian_Ratings.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omakase" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Italian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,17 +29,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,14 +56,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -578,16 +563,16 @@
         <v>3254</v>
       </c>
       <c r="K2" t="n">
-        <v>4.497</v>
+        <v>4.325</v>
       </c>
       <c r="L2" t="n">
-        <v>92.2</v>
+        <v>91.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4.66</v>
+        <v>4.482</v>
       </c>
       <c r="N2" t="n">
-        <v>83.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -630,16 +615,16 @@
         <v>1778</v>
       </c>
       <c r="K3" t="n">
-        <v>4.342</v>
+        <v>4.337</v>
       </c>
       <c r="L3" t="n">
-        <v>81.8</v>
+        <v>93.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.301</v>
+        <v>4.296</v>
       </c>
       <c r="N3" t="n">
-        <v>44.8</v>
+        <v>66</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -682,16 +667,16 @@
         <v>402</v>
       </c>
       <c r="K4" t="n">
-        <v>4.152</v>
+        <v>4.203</v>
       </c>
       <c r="L4" t="n">
-        <v>29.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>4.113</v>
+        <v>4.163</v>
       </c>
       <c r="N4" t="n">
-        <v>24.7</v>
+        <v>47.7</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -734,16 +719,16 @@
         <v>2582</v>
       </c>
       <c r="K5" t="n">
-        <v>4.369</v>
+        <v>4.318</v>
       </c>
       <c r="L5" t="n">
-        <v>85.7</v>
+        <v>90.2</v>
       </c>
       <c r="M5" t="n">
-        <v>4.415</v>
+        <v>4.363</v>
       </c>
       <c r="N5" t="n">
-        <v>60.4</v>
+        <v>72.5</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -786,16 +771,16 @@
         <v>1050</v>
       </c>
       <c r="K6" t="n">
-        <v>4.149</v>
+        <v>4.231</v>
       </c>
       <c r="L6" t="n">
-        <v>27.9</v>
+        <v>81</v>
       </c>
       <c r="M6" t="n">
-        <v>4.17</v>
+        <v>4.253</v>
       </c>
       <c r="N6" t="n">
-        <v>29.2</v>
+        <v>58.2</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -838,16 +823,16 @@
         <v>942</v>
       </c>
       <c r="K7" t="n">
-        <v>4.321</v>
+        <v>4.003</v>
       </c>
       <c r="L7" t="n">
-        <v>77.3</v>
+        <v>38.6</v>
       </c>
       <c r="M7" t="n">
-        <v>4.799</v>
+        <v>4.446</v>
       </c>
       <c r="N7" t="n">
-        <v>94.2</v>
+        <v>81</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -890,13 +875,13 @@
         <v>326</v>
       </c>
       <c r="K8" t="n">
-        <v>4.053</v>
+        <v>3.848</v>
       </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>3.016</v>
+        <v>2.864</v>
       </c>
       <c r="N8" t="n">
         <v>1.3</v>
@@ -942,16 +927,16 @@
         <v>414</v>
       </c>
       <c r="K9" t="n">
-        <v>4.096</v>
+        <v>3.964</v>
       </c>
       <c r="L9" t="n">
-        <v>20.1</v>
+        <v>26.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.039</v>
+        <v>2.942</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -994,16 +979,16 @@
         <v>1798</v>
       </c>
       <c r="K10" t="n">
-        <v>4.094</v>
+        <v>4.177</v>
       </c>
       <c r="L10" t="n">
-        <v>19.5</v>
+        <v>76.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.988</v>
+        <v>4.068</v>
       </c>
       <c r="N10" t="n">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1046,16 +1031,16 @@
         <v>1826</v>
       </c>
       <c r="K11" t="n">
-        <v>3.977</v>
+        <v>3.936</v>
       </c>
       <c r="L11" t="n">
-        <v>7.1</v>
+        <v>21.6</v>
       </c>
       <c r="M11" t="n">
-        <v>4.093</v>
+        <v>4.051</v>
       </c>
       <c r="N11" t="n">
-        <v>22.1</v>
+        <v>31.4</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1098,16 +1083,16 @@
         <v>2611</v>
       </c>
       <c r="K12" t="n">
-        <v>4.154</v>
+        <v>4.276</v>
       </c>
       <c r="L12" t="n">
-        <v>30.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>3.963</v>
+        <v>4.079</v>
       </c>
       <c r="N12" t="n">
-        <v>15.6</v>
+        <v>36.6</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1150,16 +1135,16 @@
         <v>1660</v>
       </c>
       <c r="K13" t="n">
-        <v>4.181</v>
+        <v>4.138</v>
       </c>
       <c r="L13" t="n">
-        <v>37</v>
+        <v>69.3</v>
       </c>
       <c r="M13" t="n">
-        <v>4.303</v>
+        <v>4.259</v>
       </c>
       <c r="N13" t="n">
-        <v>46.1</v>
+        <v>60.1</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1202,16 +1187,16 @@
         <v>7099</v>
       </c>
       <c r="K14" t="n">
-        <v>4.335</v>
+        <v>4.312</v>
       </c>
       <c r="L14" t="n">
-        <v>80.5</v>
+        <v>89.5</v>
       </c>
       <c r="M14" t="n">
-        <v>4.695</v>
+        <v>4.67</v>
       </c>
       <c r="N14" t="n">
-        <v>87</v>
+        <v>92.8</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1254,16 +1239,16 @@
         <v>927</v>
       </c>
       <c r="K15" t="n">
-        <v>4.265</v>
+        <v>4.019</v>
       </c>
       <c r="L15" t="n">
-        <v>63.6</v>
+        <v>43.1</v>
       </c>
       <c r="M15" t="n">
-        <v>4.096</v>
+        <v>3.86</v>
       </c>
       <c r="N15" t="n">
-        <v>22.7</v>
+        <v>17.6</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -1306,16 +1291,16 @@
         <v>724</v>
       </c>
       <c r="K16" t="n">
-        <v>4.175</v>
+        <v>3.974</v>
       </c>
       <c r="L16" t="n">
-        <v>35.7</v>
+        <v>29.4</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>3.903</v>
       </c>
       <c r="N16" t="n">
-        <v>23.4</v>
+        <v>20.9</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -1358,16 +1343,16 @@
         <v>1779</v>
       </c>
       <c r="K17" t="n">
-        <v>3.808</v>
+        <v>3.821</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.919</v>
+        <v>3.933</v>
       </c>
       <c r="N17" t="n">
-        <v>13</v>
+        <v>23.5</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -1410,16 +1395,16 @@
         <v>757</v>
       </c>
       <c r="K18" t="n">
-        <v>4.152</v>
+        <v>3.957</v>
       </c>
       <c r="L18" t="n">
-        <v>29.2</v>
+        <v>25.5</v>
       </c>
       <c r="M18" t="n">
-        <v>4.273</v>
+        <v>4.072</v>
       </c>
       <c r="N18" t="n">
-        <v>39</v>
+        <v>35.3</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -1462,16 +1447,16 @@
         <v>1031</v>
       </c>
       <c r="K19" t="n">
-        <v>4.216</v>
+        <v>4.052</v>
       </c>
       <c r="L19" t="n">
-        <v>48.1</v>
+        <v>51.6</v>
       </c>
       <c r="M19" t="n">
-        <v>4.339</v>
+        <v>4.17</v>
       </c>
       <c r="N19" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -1514,16 +1499,16 @@
         <v>633</v>
       </c>
       <c r="K20" t="n">
-        <v>4.371</v>
+        <v>4.114</v>
       </c>
       <c r="L20" t="n">
-        <v>86.40000000000001</v>
+        <v>62.7</v>
       </c>
       <c r="M20" t="n">
-        <v>4.258</v>
+        <v>4.007</v>
       </c>
       <c r="N20" t="n">
-        <v>35.7</v>
+        <v>27.5</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -1566,16 +1551,16 @@
         <v>672</v>
       </c>
       <c r="K21" t="n">
-        <v>4.037</v>
+        <v>4.175</v>
       </c>
       <c r="L21" t="n">
-        <v>11</v>
+        <v>75.8</v>
       </c>
       <c r="M21" t="n">
-        <v>4.424</v>
+        <v>4.576</v>
       </c>
       <c r="N21" t="n">
-        <v>61.7</v>
+        <v>90.8</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -1618,16 +1603,16 @@
         <v>3966</v>
       </c>
       <c r="K22" t="n">
-        <v>4.619</v>
+        <v>4.445</v>
       </c>
       <c r="L22" t="n">
         <v>98.7</v>
       </c>
       <c r="M22" t="n">
-        <v>4.754</v>
+        <v>4.574</v>
       </c>
       <c r="N22" t="n">
-        <v>91.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -1670,16 +1655,16 @@
         <v>442</v>
       </c>
       <c r="K23" t="n">
-        <v>4.647</v>
+        <v>4.197</v>
       </c>
       <c r="L23" t="n">
-        <v>99.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="M23" t="n">
-        <v>4.783</v>
+        <v>4.319</v>
       </c>
       <c r="N23" t="n">
-        <v>93.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -1722,16 +1707,16 @@
         <v>263</v>
       </c>
       <c r="K24" t="n">
-        <v>3.905</v>
+        <v>3.835</v>
       </c>
       <c r="L24" t="n">
-        <v>2.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>4.019</v>
+        <v>3.947</v>
       </c>
       <c r="N24" t="n">
-        <v>18.2</v>
+        <v>24.2</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -1774,16 +1759,16 @@
         <v>2617</v>
       </c>
       <c r="K25" t="n">
-        <v>4.408</v>
+        <v>4.431</v>
       </c>
       <c r="L25" t="n">
-        <v>87.7</v>
+        <v>98</v>
       </c>
       <c r="M25" t="n">
-        <v>4.831</v>
+        <v>4.856</v>
       </c>
       <c r="N25" t="n">
-        <v>94.8</v>
+        <v>99.3</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -1826,16 +1811,16 @@
         <v>627</v>
       </c>
       <c r="K26" t="n">
-        <v>4.242</v>
+        <v>4.023</v>
       </c>
       <c r="L26" t="n">
-        <v>57.8</v>
+        <v>44.4</v>
       </c>
       <c r="M26" t="n">
-        <v>4.132</v>
+        <v>3.919</v>
       </c>
       <c r="N26" t="n">
-        <v>27.3</v>
+        <v>22.2</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -1878,16 +1863,16 @@
         <v>11220</v>
       </c>
       <c r="K27" t="n">
-        <v>4.535</v>
+        <v>4.498</v>
       </c>
       <c r="L27" t="n">
-        <v>96.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="M27" t="n">
-        <v>4.97</v>
+        <v>4.93</v>
       </c>
       <c r="N27" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -1930,16 +1915,16 @@
         <v>468</v>
       </c>
       <c r="K28" t="n">
-        <v>4.222</v>
+        <v>4.304</v>
       </c>
       <c r="L28" t="n">
-        <v>50.6</v>
+        <v>88.2</v>
       </c>
       <c r="M28" t="n">
-        <v>4.627</v>
+        <v>4.717</v>
       </c>
       <c r="N28" t="n">
-        <v>78.59999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -1982,16 +1967,16 @@
         <v>612</v>
       </c>
       <c r="K29" t="n">
-        <v>4.138</v>
+        <v>4.266</v>
       </c>
       <c r="L29" t="n">
-        <v>24.7</v>
+        <v>84.3</v>
       </c>
       <c r="M29" t="n">
-        <v>4.259</v>
+        <v>4.39</v>
       </c>
       <c r="N29" t="n">
-        <v>36.4</v>
+        <v>75.8</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -2034,16 +2019,16 @@
         <v>876</v>
       </c>
       <c r="K30" t="n">
-        <v>4.147</v>
+        <v>4.075</v>
       </c>
       <c r="L30" t="n">
-        <v>26.6</v>
+        <v>57.5</v>
       </c>
       <c r="M30" t="n">
-        <v>4.268</v>
+        <v>4.194</v>
       </c>
       <c r="N30" t="n">
-        <v>37.7</v>
+        <v>52.9</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -2086,16 +2071,16 @@
         <v>887</v>
       </c>
       <c r="K31" t="n">
-        <v>4.263</v>
+        <v>3.757</v>
       </c>
       <c r="L31" t="n">
-        <v>62.3</v>
+        <v>5.9</v>
       </c>
       <c r="M31" t="n">
-        <v>4.387</v>
+        <v>3.866</v>
       </c>
       <c r="N31" t="n">
-        <v>57.1</v>
+        <v>18.3</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -2138,16 +2123,16 @@
         <v>1353</v>
       </c>
       <c r="K32" t="n">
-        <v>4.011</v>
+        <v>3.981</v>
       </c>
       <c r="L32" t="n">
-        <v>9.699999999999999</v>
+        <v>31.4</v>
       </c>
       <c r="M32" t="n">
-        <v>2.987</v>
+        <v>2.965</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -2190,16 +2175,16 @@
         <v>436</v>
       </c>
       <c r="K33" t="n">
-        <v>4.156</v>
+        <v>4.215</v>
       </c>
       <c r="L33" t="n">
-        <v>31.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>4.277</v>
+        <v>4.338</v>
       </c>
       <c r="N33" t="n">
-        <v>39.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -2242,16 +2227,16 @@
         <v>912</v>
       </c>
       <c r="K34" t="n">
-        <v>4.061</v>
+        <v>3.666</v>
       </c>
       <c r="L34" t="n">
-        <v>13.6</v>
+        <v>0.7</v>
       </c>
       <c r="M34" t="n">
-        <v>4.18</v>
+        <v>3.773</v>
       </c>
       <c r="N34" t="n">
-        <v>29.9</v>
+        <v>12.4</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -2294,16 +2279,16 @@
         <v>4713</v>
       </c>
       <c r="K35" t="n">
-        <v>4.191</v>
+        <v>4.018</v>
       </c>
       <c r="L35" t="n">
-        <v>40.3</v>
+        <v>42.5</v>
       </c>
       <c r="M35" t="n">
-        <v>4.975</v>
+        <v>4.77</v>
       </c>
       <c r="N35" t="n">
-        <v>98.09999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -2346,16 +2331,16 @@
         <v>910</v>
       </c>
       <c r="K36" t="n">
-        <v>4.162</v>
+        <v>3.953</v>
       </c>
       <c r="L36" t="n">
-        <v>32.5</v>
+        <v>24.2</v>
       </c>
       <c r="M36" t="n">
-        <v>4.283</v>
+        <v>4.068</v>
       </c>
       <c r="N36" t="n">
-        <v>40.9</v>
+        <v>33.3</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -2398,16 +2383,16 @@
         <v>1248</v>
       </c>
       <c r="K37" t="n">
-        <v>4.28</v>
+        <v>3.729</v>
       </c>
       <c r="L37" t="n">
-        <v>66.90000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="M37" t="n">
-        <v>4.405</v>
+        <v>3.838</v>
       </c>
       <c r="N37" t="n">
-        <v>58.4</v>
+        <v>17</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
@@ -2450,16 +2435,16 @@
         <v>235</v>
       </c>
       <c r="K38" t="n">
-        <v>3.964</v>
+        <v>3.874</v>
       </c>
       <c r="L38" t="n">
-        <v>6.5</v>
+        <v>11.8</v>
       </c>
       <c r="M38" t="n">
-        <v>4.08</v>
+        <v>3.988</v>
       </c>
       <c r="N38" t="n">
-        <v>21.4</v>
+        <v>26.1</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -2502,16 +2487,16 @@
         <v>312</v>
       </c>
       <c r="K39" t="n">
-        <v>4.21</v>
+        <v>4.003</v>
       </c>
       <c r="L39" t="n">
-        <v>46.1</v>
+        <v>37.9</v>
       </c>
       <c r="M39" t="n">
-        <v>4.333</v>
+        <v>4.12</v>
       </c>
       <c r="N39" t="n">
-        <v>49.4</v>
+        <v>43.8</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -2554,16 +2539,16 @@
         <v>3346</v>
       </c>
       <c r="K40" t="n">
-        <v>4.214</v>
+        <v>4.046</v>
       </c>
       <c r="L40" t="n">
-        <v>47.4</v>
+        <v>48.4</v>
       </c>
       <c r="M40" t="n">
-        <v>4.337</v>
+        <v>4.164</v>
       </c>
       <c r="N40" t="n">
-        <v>50</v>
+        <v>48.4</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -2606,16 +2591,16 @@
         <v>1428</v>
       </c>
       <c r="K41" t="n">
-        <v>4.313</v>
+        <v>4.135</v>
       </c>
       <c r="L41" t="n">
-        <v>75.3</v>
+        <v>66.7</v>
       </c>
       <c r="M41" t="n">
-        <v>4.727</v>
+        <v>4.532</v>
       </c>
       <c r="N41" t="n">
-        <v>90.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -2658,16 +2643,16 @@
         <v>175</v>
       </c>
       <c r="K42" t="n">
-        <v>4.228</v>
+        <v>4.125</v>
       </c>
       <c r="L42" t="n">
-        <v>53.2</v>
+        <v>64.7</v>
       </c>
       <c r="M42" t="n">
-        <v>4.351</v>
+        <v>4.246</v>
       </c>
       <c r="N42" t="n">
-        <v>52.6</v>
+        <v>56.9</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -2710,16 +2695,16 @@
         <v>279</v>
       </c>
       <c r="K43" t="n">
-        <v>4.205</v>
+        <v>4.256</v>
       </c>
       <c r="L43" t="n">
-        <v>44.2</v>
+        <v>83.7</v>
       </c>
       <c r="M43" t="n">
-        <v>4.609</v>
+        <v>4.665</v>
       </c>
       <c r="N43" t="n">
-        <v>75.3</v>
+        <v>92.2</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -2762,16 +2747,16 @@
         <v>2336</v>
       </c>
       <c r="K44" t="n">
-        <v>4.091</v>
+        <v>3.985</v>
       </c>
       <c r="L44" t="n">
-        <v>18.2</v>
+        <v>32.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.985</v>
+        <v>3.882</v>
       </c>
       <c r="N44" t="n">
-        <v>16.2</v>
+        <v>19</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -2814,16 +2799,16 @@
         <v>256</v>
       </c>
       <c r="K45" t="n">
-        <v>4.22</v>
+        <v>3.894</v>
       </c>
       <c r="L45" t="n">
-        <v>50</v>
+        <v>13.7</v>
       </c>
       <c r="M45" t="n">
-        <v>4.111</v>
+        <v>3.793</v>
       </c>
       <c r="N45" t="n">
-        <v>24</v>
+        <v>13.7</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -2866,16 +2851,16 @@
         <v>334</v>
       </c>
       <c r="K46" t="n">
-        <v>4.303</v>
+        <v>4.15</v>
       </c>
       <c r="L46" t="n">
-        <v>71.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="M46" t="n">
-        <v>4.429</v>
+        <v>4.272</v>
       </c>
       <c r="N46" t="n">
-        <v>62.3</v>
+        <v>61.4</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -2912,16 +2897,16 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>4.11</v>
+        <v>3.618</v>
       </c>
       <c r="L47" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4.23</v>
+        <v>3.724</v>
       </c>
       <c r="N47" t="n">
-        <v>33.8</v>
+        <v>11.8</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
@@ -2960,16 +2945,16 @@
         <v>1683</v>
       </c>
       <c r="K48" t="n">
-        <v>3.991</v>
+        <v>4.225</v>
       </c>
       <c r="L48" t="n">
-        <v>8.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>3.859</v>
+        <v>4.085</v>
       </c>
       <c r="N48" t="n">
-        <v>11.7</v>
+        <v>37.9</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -3012,16 +2997,16 @@
         <v>6174</v>
       </c>
       <c r="K49" t="n">
-        <v>4.527</v>
+        <v>4.175</v>
       </c>
       <c r="L49" t="n">
-        <v>94.2</v>
+        <v>75.2</v>
       </c>
       <c r="M49" t="n">
-        <v>4.659</v>
+        <v>4.297</v>
       </c>
       <c r="N49" t="n">
-        <v>82.5</v>
+        <v>66.7</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -3064,16 +3049,16 @@
         <v>508</v>
       </c>
       <c r="K50" t="n">
-        <v>3.95</v>
+        <v>3.915</v>
       </c>
       <c r="L50" t="n">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="M50" t="n">
-        <v>4.065</v>
+        <v>4.029</v>
       </c>
       <c r="N50" t="n">
-        <v>19.5</v>
+        <v>28.8</v>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -3116,16 +3101,16 @@
         <v>347</v>
       </c>
       <c r="K51" t="n">
-        <v>4.092</v>
+        <v>3.895</v>
       </c>
       <c r="L51" t="n">
-        <v>18.8</v>
+        <v>14.4</v>
       </c>
       <c r="M51" t="n">
-        <v>3.986</v>
+        <v>3.794</v>
       </c>
       <c r="N51" t="n">
-        <v>16.9</v>
+        <v>14.4</v>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -3168,16 +3153,16 @@
         <v>1813</v>
       </c>
       <c r="K52" t="n">
-        <v>4.062</v>
+        <v>4.015</v>
       </c>
       <c r="L52" t="n">
-        <v>14.9</v>
+        <v>41.8</v>
       </c>
       <c r="M52" t="n">
-        <v>3.957</v>
+        <v>3.911</v>
       </c>
       <c r="N52" t="n">
-        <v>14.9</v>
+        <v>21.6</v>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -3220,16 +3205,16 @@
         <v>3037</v>
       </c>
       <c r="K53" t="n">
-        <v>4.321</v>
+        <v>4.145</v>
       </c>
       <c r="L53" t="n">
-        <v>77.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>4.149</v>
+        <v>3.98</v>
       </c>
       <c r="N53" t="n">
-        <v>27.9</v>
+        <v>25.5</v>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -3272,16 +3257,16 @@
         <v>1238</v>
       </c>
       <c r="K54" t="n">
-        <v>4.048</v>
+        <v>3.993</v>
       </c>
       <c r="L54" t="n">
-        <v>12.3</v>
+        <v>35.3</v>
       </c>
       <c r="M54" t="n">
-        <v>3.943</v>
+        <v>3.89</v>
       </c>
       <c r="N54" t="n">
-        <v>14.3</v>
+        <v>19.6</v>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
@@ -3324,16 +3309,16 @@
         <v>99</v>
       </c>
       <c r="K55" t="n">
-        <v>4.49</v>
+        <v>4.162</v>
       </c>
       <c r="L55" t="n">
-        <v>90.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="M55" t="n">
-        <v>3.337</v>
+        <v>3.093</v>
       </c>
       <c r="N55" t="n">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -3376,16 +3361,16 @@
         <v>207</v>
       </c>
       <c r="K56" t="n">
-        <v>4.183</v>
+        <v>4.184</v>
       </c>
       <c r="L56" t="n">
-        <v>37.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>4.075</v>
+        <v>4.076</v>
       </c>
       <c r="N56" t="n">
-        <v>20.8</v>
+        <v>35.9</v>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -3428,16 +3413,16 @@
         <v>1474</v>
       </c>
       <c r="K57" t="n">
-        <v>3.958</v>
+        <v>3.93</v>
       </c>
       <c r="L57" t="n">
-        <v>5.8</v>
+        <v>19.6</v>
       </c>
       <c r="M57" t="n">
-        <v>3.856</v>
+        <v>3.829</v>
       </c>
       <c r="N57" t="n">
-        <v>11</v>
+        <v>15.7</v>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -3480,16 +3465,16 @@
         <v>933</v>
       </c>
       <c r="K58" t="n">
-        <v>4.222</v>
+        <v>3.905</v>
       </c>
       <c r="L58" t="n">
-        <v>50.6</v>
+        <v>15</v>
       </c>
       <c r="M58" t="n">
-        <v>4.345</v>
+        <v>4.019</v>
       </c>
       <c r="N58" t="n">
-        <v>51.9</v>
+        <v>28.1</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -3532,16 +3517,16 @@
         <v>2233</v>
       </c>
       <c r="K59" t="n">
-        <v>4.367</v>
+        <v>4.389</v>
       </c>
       <c r="L59" t="n">
-        <v>85.09999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="M59" t="n">
-        <v>4.254</v>
+        <v>4.276</v>
       </c>
       <c r="N59" t="n">
-        <v>35.1</v>
+        <v>62.1</v>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -3587,13 +3572,13 @@
         <v>4.319</v>
       </c>
       <c r="L60" t="n">
-        <v>76.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="M60" t="n">
         <v>4.445</v>
       </c>
       <c r="N60" t="n">
-        <v>63</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
@@ -3636,16 +3621,16 @@
         <v>422</v>
       </c>
       <c r="K61" t="n">
-        <v>4.304</v>
+        <v>4.232</v>
       </c>
       <c r="L61" t="n">
-        <v>72.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="M61" t="n">
-        <v>4.193</v>
+        <v>4.123</v>
       </c>
       <c r="N61" t="n">
-        <v>31.8</v>
+        <v>44.4</v>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
@@ -3688,16 +3673,16 @@
         <v>2721</v>
       </c>
       <c r="K62" t="n">
-        <v>4.224</v>
+        <v>4.07</v>
       </c>
       <c r="L62" t="n">
-        <v>52.6</v>
+        <v>55.6</v>
       </c>
       <c r="M62" t="n">
-        <v>4.629</v>
+        <v>4.46</v>
       </c>
       <c r="N62" t="n">
-        <v>79.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
@@ -3740,16 +3725,16 @@
         <v>309</v>
       </c>
       <c r="K63" t="n">
-        <v>4.31</v>
+        <v>4.164</v>
       </c>
       <c r="L63" t="n">
-        <v>74.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M63" t="n">
-        <v>4.724</v>
+        <v>4.564</v>
       </c>
       <c r="N63" t="n">
-        <v>89.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -3792,16 +3777,16 @@
         <v>3349</v>
       </c>
       <c r="K64" t="n">
-        <v>4.414</v>
+        <v>4.138</v>
       </c>
       <c r="L64" t="n">
-        <v>88.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M64" t="n">
-        <v>4.838</v>
+        <v>4.535</v>
       </c>
       <c r="N64" t="n">
-        <v>95.5</v>
+        <v>88.2</v>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
@@ -3844,16 +3829,16 @@
         <v>660</v>
       </c>
       <c r="K65" t="n">
-        <v>4.191</v>
+        <v>4.137</v>
       </c>
       <c r="L65" t="n">
-        <v>40.3</v>
+        <v>68</v>
       </c>
       <c r="M65" t="n">
-        <v>3.123</v>
+        <v>3.082</v>
       </c>
       <c r="N65" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -3896,16 +3881,16 @@
         <v>541</v>
       </c>
       <c r="K66" t="n">
-        <v>4.062</v>
+        <v>3.699</v>
       </c>
       <c r="L66" t="n">
-        <v>14.9</v>
+        <v>3.3</v>
       </c>
       <c r="M66" t="n">
-        <v>3.013</v>
+        <v>2.744</v>
       </c>
       <c r="N66" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -3948,16 +3933,16 @@
         <v>984</v>
       </c>
       <c r="K67" t="n">
-        <v>4.065</v>
+        <v>3.948</v>
       </c>
       <c r="L67" t="n">
-        <v>16.2</v>
+        <v>23.5</v>
       </c>
       <c r="M67" t="n">
-        <v>4.184</v>
+        <v>4.063</v>
       </c>
       <c r="N67" t="n">
-        <v>30.5</v>
+        <v>32.7</v>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -4000,16 +3985,16 @@
         <v>489</v>
       </c>
       <c r="K68" t="n">
-        <v>4.253</v>
+        <v>4.25</v>
       </c>
       <c r="L68" t="n">
-        <v>59.1</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="M68" t="n">
-        <v>4.377</v>
+        <v>4.374</v>
       </c>
       <c r="N68" t="n">
-        <v>54.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -4052,16 +4037,16 @@
         <v>2358</v>
       </c>
       <c r="K69" t="n">
-        <v>4.067</v>
+        <v>3.78</v>
       </c>
       <c r="L69" t="n">
-        <v>17.5</v>
+        <v>7.8</v>
       </c>
       <c r="M69" t="n">
-        <v>4.186</v>
+        <v>3.891</v>
       </c>
       <c r="N69" t="n">
-        <v>31.2</v>
+        <v>20.3</v>
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -4104,16 +4089,16 @@
         <v>529</v>
       </c>
       <c r="K70" t="n">
-        <v>4.025</v>
+        <v>3.932</v>
       </c>
       <c r="L70" t="n">
-        <v>10.4</v>
+        <v>20.3</v>
       </c>
       <c r="M70" t="n">
-        <v>3.921</v>
+        <v>3.83</v>
       </c>
       <c r="N70" t="n">
-        <v>13.6</v>
+        <v>16.3</v>
       </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -4156,16 +4141,16 @@
         <v>1015</v>
       </c>
       <c r="K71" t="n">
-        <v>4.27</v>
+        <v>3.689</v>
       </c>
       <c r="L71" t="n">
-        <v>65.59999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="M71" t="n">
-        <v>4.68</v>
+        <v>4.043</v>
       </c>
       <c r="N71" t="n">
-        <v>85.09999999999999</v>
+        <v>30.1</v>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -4208,16 +4193,16 @@
         <v>587</v>
       </c>
       <c r="K72" t="n">
-        <v>3.83</v>
+        <v>3.864</v>
       </c>
       <c r="L72" t="n">
-        <v>1.9</v>
+        <v>10.5</v>
       </c>
       <c r="M72" t="n">
-        <v>4.198</v>
+        <v>4.235</v>
       </c>
       <c r="N72" t="n">
-        <v>32.5</v>
+        <v>54.9</v>
       </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
@@ -4260,16 +4245,16 @@
         <v>1563</v>
       </c>
       <c r="K73" t="n">
-        <v>4.282</v>
+        <v>4.105</v>
       </c>
       <c r="L73" t="n">
-        <v>67.5</v>
+        <v>60.8</v>
       </c>
       <c r="M73" t="n">
-        <v>4.693</v>
+        <v>4.498</v>
       </c>
       <c r="N73" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -4312,16 +4297,16 @@
         <v>2277</v>
       </c>
       <c r="K74" t="n">
-        <v>4.306</v>
+        <v>4.05</v>
       </c>
       <c r="L74" t="n">
-        <v>72.7</v>
+        <v>50.3</v>
       </c>
       <c r="M74" t="n">
-        <v>4.328</v>
+        <v>4.071</v>
       </c>
       <c r="N74" t="n">
-        <v>48.1</v>
+        <v>34.6</v>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -4364,16 +4349,16 @@
         <v>1850</v>
       </c>
       <c r="K75" t="n">
-        <v>4.237</v>
+        <v>4.057</v>
       </c>
       <c r="L75" t="n">
-        <v>54.5</v>
+        <v>52.9</v>
       </c>
       <c r="M75" t="n">
-        <v>4.306</v>
+        <v>4.124</v>
       </c>
       <c r="N75" t="n">
-        <v>46.8</v>
+        <v>45.8</v>
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -4416,16 +4401,16 @@
         <v>132</v>
       </c>
       <c r="K76" t="n">
-        <v>4.204</v>
+        <v>3.958</v>
       </c>
       <c r="L76" t="n">
-        <v>43.5</v>
+        <v>26.1</v>
       </c>
       <c r="M76" t="n">
-        <v>4.204</v>
+        <v>3.958</v>
       </c>
       <c r="N76" t="n">
-        <v>33.1</v>
+        <v>24.8</v>
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -4468,16 +4453,16 @@
         <v>1322</v>
       </c>
       <c r="K77" t="n">
-        <v>4.196</v>
+        <v>4.051</v>
       </c>
       <c r="L77" t="n">
-        <v>41.6</v>
+        <v>51</v>
       </c>
       <c r="M77" t="n">
-        <v>4.318</v>
+        <v>4.169</v>
       </c>
       <c r="N77" t="n">
-        <v>47.4</v>
+        <v>49.7</v>
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -4520,16 +4505,16 @@
         <v>1598</v>
       </c>
       <c r="K78" t="n">
-        <v>4.58</v>
+        <v>4.223</v>
       </c>
       <c r="L78" t="n">
-        <v>97.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="M78" t="n">
-        <v>4.714</v>
+        <v>4.346</v>
       </c>
       <c r="N78" t="n">
-        <v>87.7</v>
+        <v>71.2</v>
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -4572,16 +4557,16 @@
         <v>440</v>
       </c>
       <c r="K79" t="n">
-        <v>4.217</v>
+        <v>3.987</v>
       </c>
       <c r="L79" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="M79" t="n">
-        <v>4.34</v>
+        <v>4.104</v>
       </c>
       <c r="N79" t="n">
-        <v>51.3</v>
+        <v>40.5</v>
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
@@ -4624,16 +4609,16 @@
         <v>434</v>
       </c>
       <c r="K80" t="n">
-        <v>4.136</v>
+        <v>3.909</v>
       </c>
       <c r="L80" t="n">
-        <v>24</v>
+        <v>16.3</v>
       </c>
       <c r="M80" t="n">
-        <v>4.533</v>
+        <v>4.285</v>
       </c>
       <c r="N80" t="n">
-        <v>69.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
@@ -4676,16 +4661,16 @@
         <v>440</v>
       </c>
       <c r="K81" t="n">
-        <v>4.217</v>
+        <v>4.023</v>
       </c>
       <c r="L81" t="n">
-        <v>48.7</v>
+        <v>45.1</v>
       </c>
       <c r="M81" t="n">
-        <v>4.622</v>
+        <v>4.409</v>
       </c>
       <c r="N81" t="n">
-        <v>77.3</v>
+        <v>77.8</v>
       </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -4728,16 +4713,16 @@
         <v>1465</v>
       </c>
       <c r="K82" t="n">
+        <v>4.107</v>
+      </c>
+      <c r="L82" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="M82" t="n">
         <v>4.288</v>
       </c>
-      <c r="L82" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="M82" t="n">
-        <v>4.477</v>
-      </c>
       <c r="N82" t="n">
-        <v>66.2</v>
+        <v>64.7</v>
       </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
@@ -4780,16 +4765,16 @@
         <v>683</v>
       </c>
       <c r="K83" t="n">
-        <v>4.269</v>
+        <v>4.026</v>
       </c>
       <c r="L83" t="n">
-        <v>64.90000000000001</v>
+        <v>45.8</v>
       </c>
       <c r="M83" t="n">
-        <v>5.068</v>
+        <v>4.779</v>
       </c>
       <c r="N83" t="n">
-        <v>99.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
@@ -4832,16 +4817,16 @@
         <v>597</v>
       </c>
       <c r="K84" t="n">
-        <v>4.279</v>
+        <v>4.056</v>
       </c>
       <c r="L84" t="n">
-        <v>66.2</v>
+        <v>52.3</v>
       </c>
       <c r="M84" t="n">
-        <v>4.404</v>
+        <v>4.175</v>
       </c>
       <c r="N84" t="n">
-        <v>57.8</v>
+        <v>51</v>
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
@@ -4884,16 +4869,16 @@
         <v>419</v>
       </c>
       <c r="K85" t="n">
-        <v>4.467</v>
+        <v>4.356</v>
       </c>
       <c r="L85" t="n">
-        <v>89.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="M85" t="n">
-        <v>4.597</v>
+        <v>4.483</v>
       </c>
       <c r="N85" t="n">
-        <v>72.7</v>
+        <v>85</v>
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
@@ -4936,16 +4921,16 @@
         <v>3059</v>
       </c>
       <c r="K86" t="n">
-        <v>4.261</v>
+        <v>4.306</v>
       </c>
       <c r="L86" t="n">
-        <v>61.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M86" t="n">
-        <v>4.385</v>
+        <v>4.432</v>
       </c>
       <c r="N86" t="n">
-        <v>56.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
@@ -4988,16 +4973,16 @@
         <v>673</v>
       </c>
       <c r="K87" t="n">
-        <v>4.351</v>
+        <v>4.013</v>
       </c>
       <c r="L87" t="n">
-        <v>83.09999999999999</v>
+        <v>40.5</v>
       </c>
       <c r="M87" t="n">
-        <v>4.478</v>
+        <v>4.13</v>
       </c>
       <c r="N87" t="n">
-        <v>66.90000000000001</v>
+        <v>47.1</v>
       </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
@@ -5040,16 +5025,16 @@
         <v>535</v>
       </c>
       <c r="K88" t="n">
-        <v>4.336</v>
+        <v>4.015</v>
       </c>
       <c r="L88" t="n">
-        <v>81.2</v>
+        <v>41.2</v>
       </c>
       <c r="M88" t="n">
-        <v>3.229</v>
+        <v>2.99</v>
       </c>
       <c r="N88" t="n">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
@@ -5092,16 +5077,16 @@
         <v>285</v>
       </c>
       <c r="K89" t="n">
-        <v>4.116</v>
+        <v>3.994</v>
       </c>
       <c r="L89" t="n">
-        <v>22.7</v>
+        <v>36.6</v>
       </c>
       <c r="M89" t="n">
-        <v>4.236</v>
+        <v>4.11</v>
       </c>
       <c r="N89" t="n">
-        <v>34.4</v>
+        <v>42.5</v>
       </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
@@ -5144,16 +5129,16 @@
         <v>90</v>
       </c>
       <c r="K90" t="n">
-        <v>4.603</v>
+        <v>4.131</v>
       </c>
       <c r="L90" t="n">
-        <v>98.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M90" t="n">
-        <v>4.737</v>
+        <v>4.251</v>
       </c>
       <c r="N90" t="n">
-        <v>90.90000000000001</v>
+        <v>57.5</v>
       </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
@@ -5196,16 +5181,16 @@
         <v>422</v>
       </c>
       <c r="K91" t="n">
-        <v>4.534</v>
+        <v>4.171</v>
       </c>
       <c r="L91" t="n">
-        <v>95.5</v>
+        <v>74.5</v>
       </c>
       <c r="M91" t="n">
-        <v>4.666</v>
+        <v>4.293</v>
       </c>
       <c r="N91" t="n">
-        <v>83.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
@@ -5248,16 +5233,16 @@
         <v>525</v>
       </c>
       <c r="K92" t="n">
-        <v>4.548</v>
+        <v>4.417</v>
       </c>
       <c r="L92" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="M92" t="n">
-        <v>4.984</v>
+        <v>4.841</v>
       </c>
       <c r="N92" t="n">
-        <v>98.7</v>
+        <v>98</v>
       </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -5300,16 +5285,16 @@
         <v>2137</v>
       </c>
       <c r="K93" t="n">
-        <v>4.155</v>
+        <v>4.066</v>
       </c>
       <c r="L93" t="n">
-        <v>31.2</v>
+        <v>54.2</v>
       </c>
       <c r="M93" t="n">
-        <v>4.554</v>
+        <v>4.456</v>
       </c>
       <c r="N93" t="n">
-        <v>70.8</v>
+        <v>81.7</v>
       </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -5352,16 +5337,16 @@
         <v>41</v>
       </c>
       <c r="K94" t="n">
-        <v>3.795</v>
+        <v>3.993</v>
       </c>
       <c r="L94" t="n">
-        <v>0.6</v>
+        <v>35.9</v>
       </c>
       <c r="M94" t="n">
-        <v>3.906</v>
+        <v>4.11</v>
       </c>
       <c r="N94" t="n">
-        <v>12.3</v>
+        <v>41.8</v>
       </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -5404,16 +5389,16 @@
         <v>2313</v>
       </c>
       <c r="K95" t="n">
-        <v>4.187</v>
+        <v>4.072</v>
       </c>
       <c r="L95" t="n">
-        <v>38.3</v>
+        <v>56.9</v>
       </c>
       <c r="M95" t="n">
-        <v>4.589</v>
+        <v>4.463</v>
       </c>
       <c r="N95" t="n">
-        <v>71.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -5456,16 +5441,16 @@
         <v>1632</v>
       </c>
       <c r="K96" t="n">
-        <v>4.19</v>
+        <v>3.972</v>
       </c>
       <c r="L96" t="n">
-        <v>39.6</v>
+        <v>28.8</v>
       </c>
       <c r="M96" t="n">
-        <v>3.12</v>
+        <v>2.958</v>
       </c>
       <c r="N96" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -5508,16 +5493,16 @@
         <v>11345</v>
       </c>
       <c r="K97" t="n">
-        <v>4.498</v>
+        <v>4.334</v>
       </c>
       <c r="L97" t="n">
-        <v>92.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="M97" t="n">
-        <v>3.344</v>
+        <v>3.222</v>
       </c>
       <c r="N97" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -5560,16 +5545,16 @@
         <v>392</v>
       </c>
       <c r="K98" t="n">
-        <v>4.207</v>
+        <v>3.924</v>
       </c>
       <c r="L98" t="n">
-        <v>45.5</v>
+        <v>17.6</v>
       </c>
       <c r="M98" t="n">
-        <v>4.33</v>
+        <v>4.039</v>
       </c>
       <c r="N98" t="n">
-        <v>48.7</v>
+        <v>29.4</v>
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
@@ -5612,16 +5597,16 @@
         <v>774</v>
       </c>
       <c r="K99" t="n">
-        <v>4.255</v>
+        <v>4.292</v>
       </c>
       <c r="L99" t="n">
-        <v>60.4</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="M99" t="n">
-        <v>3.155</v>
+        <v>3.182</v>
       </c>
       <c r="N99" t="n">
-        <v>5.8</v>
+        <v>8.5</v>
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
@@ -5664,16 +5649,16 @@
         <v>541</v>
       </c>
       <c r="K100" t="n">
-        <v>4.313</v>
+        <v>4.089</v>
       </c>
       <c r="L100" t="n">
-        <v>75.3</v>
+        <v>59.5</v>
       </c>
       <c r="M100" t="n">
-        <v>3.202</v>
+        <v>3.036</v>
       </c>
       <c r="N100" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -5716,16 +5701,16 @@
         <v>2884</v>
       </c>
       <c r="K101" t="n">
-        <v>4.065</v>
+        <v>3.759</v>
       </c>
       <c r="L101" t="n">
-        <v>16.2</v>
+        <v>6.5</v>
       </c>
       <c r="M101" t="n">
-        <v>3.023</v>
+        <v>2.796</v>
       </c>
       <c r="N101" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
@@ -5768,16 +5753,16 @@
         <v>1736</v>
       </c>
       <c r="K102" t="n">
-        <v>4.329</v>
+        <v>4.135</v>
       </c>
       <c r="L102" t="n">
-        <v>79.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="M102" t="n">
-        <v>4.455</v>
+        <v>4.256</v>
       </c>
       <c r="N102" t="n">
-        <v>65.59999999999999</v>
+        <v>59.5</v>
       </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
@@ -5820,16 +5805,16 @@
         <v>4643</v>
       </c>
       <c r="K103" t="n">
-        <v>4.223</v>
+        <v>4.069</v>
       </c>
       <c r="L103" t="n">
-        <v>51.9</v>
+        <v>54.9</v>
       </c>
       <c r="M103" t="n">
-        <v>4.628</v>
+        <v>4.459</v>
       </c>
       <c r="N103" t="n">
-        <v>79.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -5872,16 +5857,16 @@
         <v>616</v>
       </c>
       <c r="K104" t="n">
-        <v>4.241</v>
+        <v>3.684</v>
       </c>
       <c r="L104" t="n">
-        <v>57.1</v>
+        <v>2</v>
       </c>
       <c r="M104" t="n">
-        <v>4.131</v>
+        <v>3.589</v>
       </c>
       <c r="N104" t="n">
-        <v>26.6</v>
+        <v>10.5</v>
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
@@ -5924,16 +5909,16 @@
         <v>2380</v>
       </c>
       <c r="K105" t="n">
-        <v>4.238</v>
+        <v>4.104</v>
       </c>
       <c r="L105" t="n">
-        <v>55.8</v>
+        <v>60.1</v>
       </c>
       <c r="M105" t="n">
-        <v>3.147</v>
+        <v>3.047</v>
       </c>
       <c r="N105" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
@@ -5976,16 +5961,16 @@
         <v>1336</v>
       </c>
       <c r="K106" t="n">
-        <v>4.283</v>
+        <v>4.046</v>
       </c>
       <c r="L106" t="n">
-        <v>68.8</v>
+        <v>49</v>
       </c>
       <c r="M106" t="n">
-        <v>4.408</v>
+        <v>4.164</v>
       </c>
       <c r="N106" t="n">
-        <v>59.1</v>
+        <v>49</v>
       </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -6028,16 +6013,16 @@
         <v>643</v>
       </c>
       <c r="K107" t="n">
-        <v>4.061</v>
+        <v>3.929</v>
       </c>
       <c r="L107" t="n">
-        <v>13.6</v>
+        <v>18.3</v>
       </c>
       <c r="M107" t="n">
-        <v>4.451</v>
+        <v>4.306</v>
       </c>
       <c r="N107" t="n">
-        <v>64.3</v>
+        <v>67.3</v>
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -6080,16 +6065,16 @@
         <v>756</v>
       </c>
       <c r="K108" t="n">
-        <v>4.254</v>
+        <v>3.675</v>
       </c>
       <c r="L108" t="n">
-        <v>59.7</v>
+        <v>1.3</v>
       </c>
       <c r="M108" t="n">
-        <v>4.378</v>
+        <v>3.782</v>
       </c>
       <c r="N108" t="n">
-        <v>55.2</v>
+        <v>13.1</v>
       </c>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
@@ -6132,16 +6117,16 @@
         <v>1049</v>
       </c>
       <c r="K109" t="n">
-        <v>4.17</v>
+        <v>3.985</v>
       </c>
       <c r="L109" t="n">
-        <v>33.1</v>
+        <v>32</v>
       </c>
       <c r="M109" t="n">
-        <v>4.292</v>
+        <v>4.101</v>
       </c>
       <c r="N109" t="n">
-        <v>41.6</v>
+        <v>39.9</v>
       </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
@@ -6184,16 +6169,16 @@
         <v>1217</v>
       </c>
       <c r="K110" t="n">
-        <v>4.362</v>
+        <v>4.124</v>
       </c>
       <c r="L110" t="n">
-        <v>84.40000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="M110" t="n">
-        <v>4.489</v>
+        <v>4.244</v>
       </c>
       <c r="N110" t="n">
-        <v>67.5</v>
+        <v>56.2</v>
       </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
@@ -6236,16 +6221,16 @@
         <v>797</v>
       </c>
       <c r="K111" t="n">
-        <v>4.257</v>
+        <v>4.008</v>
       </c>
       <c r="L111" t="n">
-        <v>61</v>
+        <v>39.9</v>
       </c>
       <c r="M111" t="n">
-        <v>4.381</v>
+        <v>4.125</v>
       </c>
       <c r="N111" t="n">
-        <v>55.8</v>
+        <v>46.4</v>
       </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
@@ -6288,16 +6273,16 @@
         <v>3165</v>
       </c>
       <c r="K112" t="n">
-        <v>3.915</v>
+        <v>3.908</v>
       </c>
       <c r="L112" t="n">
-        <v>3.2</v>
+        <v>15.7</v>
       </c>
       <c r="M112" t="n">
-        <v>3.814</v>
+        <v>3.807</v>
       </c>
       <c r="N112" t="n">
-        <v>10.4</v>
+        <v>15</v>
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
@@ -6340,16 +6325,16 @@
         <v>6811</v>
       </c>
       <c r="K113" t="n">
-        <v>4.205</v>
+        <v>4.302</v>
       </c>
       <c r="L113" t="n">
-        <v>44.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="M113" t="n">
-        <v>4.609</v>
+        <v>4.715</v>
       </c>
       <c r="N113" t="n">
-        <v>75.3</v>
+        <v>94.8</v>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
@@ -6392,16 +6377,16 @@
         <v>9611</v>
       </c>
       <c r="K114" t="n">
-        <v>3.92</v>
+        <v>3.725</v>
       </c>
       <c r="L114" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="M114" t="n">
-        <v>4.296</v>
+        <v>4.082</v>
       </c>
       <c r="N114" t="n">
-        <v>44.2</v>
+        <v>37.3</v>
       </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
@@ -6444,16 +6429,16 @@
         <v>3310</v>
       </c>
       <c r="K115" t="n">
-        <v>4.172</v>
+        <v>4.085</v>
       </c>
       <c r="L115" t="n">
-        <v>35.1</v>
+        <v>58.2</v>
       </c>
       <c r="M115" t="n">
-        <v>4.294</v>
+        <v>4.204</v>
       </c>
       <c r="N115" t="n">
-        <v>43.5</v>
+        <v>53.6</v>
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
@@ -6496,16 +6481,16 @@
         <v>1492</v>
       </c>
       <c r="K116" t="n">
-        <v>4.491</v>
+        <v>4.157</v>
       </c>
       <c r="L116" t="n">
-        <v>91.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="M116" t="n">
-        <v>4.622</v>
+        <v>4.278</v>
       </c>
       <c r="N116" t="n">
-        <v>77.3</v>
+        <v>62.7</v>
       </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
@@ -6548,13 +6533,13 @@
         <v>1549</v>
       </c>
       <c r="K117" t="n">
-        <v>4.245</v>
+        <v>4.085</v>
       </c>
       <c r="L117" t="n">
-        <v>58.4</v>
+        <v>58.8</v>
       </c>
       <c r="M117" t="n">
-        <v>3.151</v>
+        <v>3.033</v>
       </c>
       <c r="N117" t="n">
         <v>5.2</v>
@@ -6600,16 +6585,16 @@
         <v>480</v>
       </c>
       <c r="K118" t="n">
-        <v>4.328</v>
+        <v>4.002</v>
       </c>
       <c r="L118" t="n">
-        <v>79.2</v>
+        <v>37.3</v>
       </c>
       <c r="M118" t="n">
-        <v>4.454</v>
+        <v>4.119</v>
       </c>
       <c r="N118" t="n">
-        <v>64.90000000000001</v>
+        <v>43.1</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
@@ -6652,16 +6637,16 @@
         <v>575</v>
       </c>
       <c r="K119" t="n">
-        <v>4.237</v>
+        <v>3.986</v>
       </c>
       <c r="L119" t="n">
-        <v>54.5</v>
+        <v>33.3</v>
       </c>
       <c r="M119" t="n">
-        <v>4.644</v>
+        <v>4.368</v>
       </c>
       <c r="N119" t="n">
-        <v>80.5</v>
+        <v>73.2</v>
       </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
@@ -6704,16 +6689,16 @@
         <v>1146</v>
       </c>
       <c r="K120" t="n">
-        <v>4.309</v>
+        <v>4.125</v>
       </c>
       <c r="L120" t="n">
-        <v>74</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M120" t="n">
-        <v>4.722</v>
+        <v>4.52</v>
       </c>
       <c r="N120" t="n">
-        <v>89</v>
+        <v>86.3</v>
       </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
@@ -6756,16 +6741,16 @@
         <v>676</v>
       </c>
       <c r="K121" t="n">
-        <v>4.21</v>
+        <v>4.328</v>
       </c>
       <c r="L121" t="n">
-        <v>46.1</v>
+        <v>92.2</v>
       </c>
       <c r="M121" t="n">
-        <v>4.614</v>
+        <v>4.743</v>
       </c>
       <c r="N121" t="n">
-        <v>76.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
@@ -6808,16 +6793,16 @@
         <v>3068</v>
       </c>
       <c r="K122" t="n">
-        <v>4.513</v>
+        <v>4.448</v>
       </c>
       <c r="L122" t="n">
-        <v>93.5</v>
+        <v>99.3</v>
       </c>
       <c r="M122" t="n">
-        <v>4.645</v>
+        <v>4.578</v>
       </c>
       <c r="N122" t="n">
-        <v>81.2</v>
+        <v>91.5</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
@@ -6860,16 +6845,16 @@
         <v>731</v>
       </c>
       <c r="K123" t="n">
-        <v>4.149</v>
+        <v>4.279</v>
       </c>
       <c r="L123" t="n">
-        <v>27.9</v>
+        <v>86.3</v>
       </c>
       <c r="M123" t="n">
-        <v>4.27</v>
+        <v>4.404</v>
       </c>
       <c r="N123" t="n">
-        <v>38.3</v>
+        <v>76.5</v>
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
@@ -6912,16 +6897,16 @@
         <v>243</v>
       </c>
       <c r="K124" t="n">
-        <v>3.95</v>
+        <v>4.159</v>
       </c>
       <c r="L124" t="n">
-        <v>4.5</v>
+        <v>72.5</v>
       </c>
       <c r="M124" t="n">
-        <v>4.065</v>
+        <v>4.28</v>
       </c>
       <c r="N124" t="n">
-        <v>19.5</v>
+        <v>63.4</v>
       </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
@@ -6964,16 +6949,16 @@
         <v>597</v>
       </c>
       <c r="K125" t="n">
-        <v>4.239</v>
+        <v>4.023</v>
       </c>
       <c r="L125" t="n">
-        <v>56.5</v>
+        <v>43.8</v>
       </c>
       <c r="M125" t="n">
-        <v>4.646</v>
+        <v>4.409</v>
       </c>
       <c r="N125" t="n">
-        <v>81.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
@@ -7016,16 +7001,16 @@
         <v>130</v>
       </c>
       <c r="K126" t="n">
-        <v>4.532</v>
+        <v>4.036</v>
       </c>
       <c r="L126" t="n">
-        <v>94.8</v>
+        <v>47.7</v>
       </c>
       <c r="M126" t="n">
-        <v>4.415</v>
+        <v>3.931</v>
       </c>
       <c r="N126" t="n">
-        <v>60.4</v>
+        <v>22.9</v>
       </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -7068,16 +7053,16 @@
         <v>611</v>
       </c>
       <c r="K127" t="n">
-        <v>4.138</v>
+        <v>4.256</v>
       </c>
       <c r="L127" t="n">
-        <v>24.7</v>
+        <v>83</v>
       </c>
       <c r="M127" t="n">
-        <v>4.259</v>
+        <v>4.38</v>
       </c>
       <c r="N127" t="n">
-        <v>36.4</v>
+        <v>74.5</v>
       </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
@@ -7120,16 +7105,16 @@
         <v>1019</v>
       </c>
       <c r="K128" t="n">
-        <v>4.476</v>
+        <v>4.107</v>
       </c>
       <c r="L128" t="n">
-        <v>90.3</v>
+        <v>61.4</v>
       </c>
       <c r="M128" t="n">
-        <v>4.607</v>
+        <v>4.227</v>
       </c>
       <c r="N128" t="n">
-        <v>74.7</v>
+        <v>54.2</v>
       </c>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
@@ -7172,16 +7157,16 @@
         <v>1773</v>
       </c>
       <c r="K129" t="n">
-        <v>4.395</v>
+        <v>4.38</v>
       </c>
       <c r="L129" t="n">
-        <v>87</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="M129" t="n">
-        <v>4.281</v>
+        <v>4.267</v>
       </c>
       <c r="N129" t="n">
-        <v>40.3</v>
+        <v>60.8</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -7224,16 +7209,16 @@
         <v>3285</v>
       </c>
       <c r="K130" t="n">
-        <v>4.187</v>
+        <v>4.048</v>
       </c>
       <c r="L130" t="n">
-        <v>38.3</v>
+        <v>49.7</v>
       </c>
       <c r="M130" t="n">
-        <v>4.589</v>
+        <v>4.436</v>
       </c>
       <c r="N130" t="n">
-        <v>71.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -7276,16 +7261,16 @@
         <v>1064</v>
       </c>
       <c r="K131" t="n">
-        <v>4.171</v>
+        <v>3.945</v>
       </c>
       <c r="L131" t="n">
-        <v>34.4</v>
+        <v>22.2</v>
       </c>
       <c r="M131" t="n">
-        <v>4.293</v>
+        <v>4.06</v>
       </c>
       <c r="N131" t="n">
-        <v>42.9</v>
+        <v>32</v>
       </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
@@ -7328,16 +7313,16 @@
         <v>931</v>
       </c>
       <c r="K132" t="n">
-        <v>3.761</v>
+        <v>3.762</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M132" t="n">
-        <v>4.122</v>
+        <v>4.123</v>
       </c>
       <c r="N132" t="n">
-        <v>25.3</v>
+        <v>45.1</v>
       </c>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
@@ -7380,16 +7365,16 @@
         <v>1298</v>
       </c>
       <c r="K133" t="n">
-        <v>4.18</v>
+        <v>3.976</v>
       </c>
       <c r="L133" t="n">
-        <v>36.4</v>
+        <v>30.1</v>
       </c>
       <c r="M133" t="n">
-        <v>4.302</v>
+        <v>4.092</v>
       </c>
       <c r="N133" t="n">
-        <v>45.5</v>
+        <v>39.2</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
@@ -7432,16 +7417,16 @@
         <v>579</v>
       </c>
       <c r="K134" t="n">
-        <v>4.134</v>
+        <v>3.97</v>
       </c>
       <c r="L134" t="n">
-        <v>23.4</v>
+        <v>27.5</v>
       </c>
       <c r="M134" t="n">
-        <v>4.907</v>
+        <v>4.712</v>
       </c>
       <c r="N134" t="n">
-        <v>96.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -7484,16 +7469,16 @@
         <v>118</v>
       </c>
       <c r="K135" t="n">
-        <v>4.282</v>
+        <v>4.149</v>
       </c>
       <c r="L135" t="n">
-        <v>67.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="M135" t="n">
-        <v>4.693</v>
+        <v>4.547</v>
       </c>
       <c r="N135" t="n">
-        <v>85.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -7536,16 +7521,16 @@
         <v>893</v>
       </c>
       <c r="K136" t="n">
-        <v>4.263</v>
+        <v>4.269</v>
       </c>
       <c r="L136" t="n">
-        <v>62.3</v>
+        <v>85</v>
       </c>
       <c r="M136" t="n">
-        <v>4.672</v>
+        <v>4.679</v>
       </c>
       <c r="N136" t="n">
-        <v>84.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -7588,16 +7573,16 @@
         <v>4111</v>
       </c>
       <c r="K137" t="n">
-        <v>4.306</v>
+        <v>4.133</v>
       </c>
       <c r="L137" t="n">
-        <v>72.7</v>
+        <v>66</v>
       </c>
       <c r="M137" t="n">
-        <v>4.719</v>
+        <v>4.529</v>
       </c>
       <c r="N137" t="n">
-        <v>88.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
@@ -7640,16 +7625,16 @@
         <v>707</v>
       </c>
       <c r="K138" t="n">
-        <v>4.147</v>
+        <v>3.956</v>
       </c>
       <c r="L138" t="n">
-        <v>26.6</v>
+        <v>24.8</v>
       </c>
       <c r="M138" t="n">
-        <v>4.545</v>
+        <v>4.335</v>
       </c>
       <c r="N138" t="n">
-        <v>70.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -7692,16 +7677,16 @@
         <v>555</v>
       </c>
       <c r="K139" t="n">
-        <v>4.234</v>
+        <v>3.992</v>
       </c>
       <c r="L139" t="n">
-        <v>53.9</v>
+        <v>34.6</v>
       </c>
       <c r="M139" t="n">
-        <v>4.358</v>
+        <v>4.109</v>
       </c>
       <c r="N139" t="n">
-        <v>53.2</v>
+        <v>41.2</v>
       </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
@@ -7744,16 +7729,16 @@
         <v>972</v>
       </c>
       <c r="K140" t="n">
-        <v>4.268</v>
+        <v>4.027</v>
       </c>
       <c r="L140" t="n">
-        <v>64.3</v>
+        <v>46.4</v>
       </c>
       <c r="M140" t="n">
-        <v>3.169</v>
+        <v>2.991</v>
       </c>
       <c r="N140" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -7796,16 +7781,16 @@
         <v>1046</v>
       </c>
       <c r="K141" t="n">
-        <v>4.17</v>
+        <v>3.972</v>
       </c>
       <c r="L141" t="n">
-        <v>33.1</v>
+        <v>28.1</v>
       </c>
       <c r="M141" t="n">
-        <v>4.292</v>
+        <v>4.088</v>
       </c>
       <c r="N141" t="n">
-        <v>41.6</v>
+        <v>38.6</v>
       </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -7848,16 +7833,16 @@
         <v>1561</v>
       </c>
       <c r="K142" t="n">
-        <v>4.289</v>
+        <v>4.064</v>
       </c>
       <c r="L142" t="n">
-        <v>70.09999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="M142" t="n">
-        <v>4.414</v>
+        <v>4.183</v>
       </c>
       <c r="N142" t="n">
-        <v>59.7</v>
+        <v>51.6</v>
       </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
@@ -7900,16 +7885,16 @@
         <v>546</v>
       </c>
       <c r="K143" t="n">
-        <v>4.114</v>
+        <v>3.945</v>
       </c>
       <c r="L143" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="M143" t="n">
-        <v>4.509</v>
+        <v>4.324</v>
       </c>
       <c r="N143" t="n">
-        <v>68.8</v>
+        <v>69.3</v>
       </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
@@ -7952,16 +7937,16 @@
         <v>1959</v>
       </c>
       <c r="K144" t="n">
-        <v>4.197</v>
+        <v>4.005</v>
       </c>
       <c r="L144" t="n">
-        <v>42.2</v>
+        <v>39.2</v>
       </c>
       <c r="M144" t="n">
-        <v>4.6</v>
+        <v>4.389</v>
       </c>
       <c r="N144" t="n">
-        <v>73.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
@@ -8004,16 +7989,16 @@
         <v>1606</v>
       </c>
       <c r="K145" t="n">
-        <v>4.431</v>
+        <v>4.42</v>
       </c>
       <c r="L145" t="n">
-        <v>89</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="M145" t="n">
-        <v>4.856</v>
+        <v>4.844</v>
       </c>
       <c r="N145" t="n">
-        <v>96.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
@@ -8056,16 +8041,16 @@
         <v>639</v>
       </c>
       <c r="K146" t="n">
-        <v>4.038</v>
+        <v>3.884</v>
       </c>
       <c r="L146" t="n">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="M146" t="n">
-        <v>4.156</v>
+        <v>3.997</v>
       </c>
       <c r="N146" t="n">
-        <v>28.6</v>
+        <v>26.8</v>
       </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -8108,16 +8093,16 @@
         <v>685</v>
       </c>
       <c r="K147" t="n">
-        <v>4.352</v>
+        <v>4.033</v>
       </c>
       <c r="L147" t="n">
-        <v>83.8</v>
+        <v>47.1</v>
       </c>
       <c r="M147" t="n">
-        <v>4.77</v>
+        <v>4.42</v>
       </c>
       <c r="N147" t="n">
-        <v>92.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
@@ -8160,16 +8145,16 @@
         <v>429</v>
       </c>
       <c r="K148" t="n">
-        <v>4.111</v>
+        <v>3.883</v>
       </c>
       <c r="L148" t="n">
-        <v>21.4</v>
+        <v>12.4</v>
       </c>
       <c r="M148" t="n">
-        <v>4.505</v>
+        <v>4.256</v>
       </c>
       <c r="N148" t="n">
-        <v>68.2</v>
+        <v>58.8</v>
       </c>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
@@ -8212,16 +8197,16 @@
         <v>433</v>
       </c>
       <c r="K149" t="n">
-        <v>4.008</v>
+        <v>3.93</v>
       </c>
       <c r="L149" t="n">
-        <v>9.1</v>
+        <v>19</v>
       </c>
       <c r="M149" t="n">
-        <v>4.125</v>
+        <v>4.045</v>
       </c>
       <c r="N149" t="n">
-        <v>26</v>
+        <v>30.7</v>
       </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
@@ -8264,16 +8249,16 @@
         <v>1327</v>
       </c>
       <c r="K150" t="n">
-        <v>3.98</v>
+        <v>3.867</v>
       </c>
       <c r="L150" t="n">
-        <v>7.8</v>
+        <v>11.1</v>
       </c>
       <c r="M150" t="n">
-        <v>4.362</v>
+        <v>4.238</v>
       </c>
       <c r="N150" t="n">
-        <v>53.9</v>
+        <v>55.6</v>
       </c>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
@@ -8316,16 +8301,16 @@
         <v>4784</v>
       </c>
       <c r="K151" t="n">
-        <v>4.322</v>
+        <v>4.071</v>
       </c>
       <c r="L151" t="n">
-        <v>78.59999999999999</v>
+        <v>56.2</v>
       </c>
       <c r="M151" t="n">
-        <v>4.448</v>
+        <v>4.19</v>
       </c>
       <c r="N151" t="n">
-        <v>63.6</v>
+        <v>52.3</v>
       </c>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -8368,16 +8353,16 @@
         <v>1821</v>
       </c>
       <c r="K152" t="n">
-        <v>4.298</v>
+        <v>4.343</v>
       </c>
       <c r="L152" t="n">
-        <v>70.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="M152" t="n">
-        <v>3.192</v>
+        <v>3.225</v>
       </c>
       <c r="N152" t="n">
-        <v>7.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
@@ -8420,16 +8405,16 @@
         <v>10743</v>
       </c>
       <c r="K153" t="n">
-        <v>4.14</v>
+        <v>3.715</v>
       </c>
       <c r="L153" t="n">
-        <v>26</v>
+        <v>3.9</v>
       </c>
       <c r="M153" t="n">
-        <v>4.033</v>
+        <v>3.619</v>
       </c>
       <c r="N153" t="n">
-        <v>18.8</v>
+        <v>11.1</v>
       </c>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
@@ -8472,16 +8457,16 @@
         <v>365</v>
       </c>
       <c r="K154" t="n">
-        <v>4.201</v>
+        <v>3.934</v>
       </c>
       <c r="L154" t="n">
-        <v>42.9</v>
+        <v>20.9</v>
       </c>
       <c r="M154" t="n">
-        <v>4.604</v>
+        <v>4.311</v>
       </c>
       <c r="N154" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
@@ -8524,193 +8509,21 @@
         <v>641</v>
       </c>
       <c r="K155" t="n">
-        <v>4.348</v>
+        <v>3.98</v>
       </c>
       <c r="L155" t="n">
-        <v>82.5</v>
+        <v>30.7</v>
       </c>
       <c r="M155" t="n">
-        <v>4.765</v>
+        <v>4.362</v>
       </c>
       <c r="N155" t="n">
-        <v>92.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Fratelli Italian Restaurant</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Omakase Value Score Methodology (v2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>1. Google Bias Correction</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   correction_factor = 0.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   corrected_rating = raw_google_rating * correction_factor</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Google Maps ratings are systematically inflated. This corrects by ~3%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2. Wilson Score Lower Bound (Rating Adjustment)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   z = 1.96 (95% confidence interval)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Converts 5-star to proportion, computes Wilson lower bound, converts back.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Effect: statistically rigorous penalty for low review counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Unlike Bayesian average, penalty is based on actual statistical uncertainty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>3. Price Exponent (Empirically Derived)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Derived via log-log regression: log(rating) ~ beta * log(price)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   The regression coefficient |beta| becomes the exponent, capped to [0.1, 0.6].</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>4. Value Score</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   value = adj_rating * (100 / price) ^ exponent</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Higher score = better combination of quality and affordability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>5. Percentile Ranking</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Rating Pctl: where adjusted rating falls vs all others (0=worst, 100=best)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Value Pctl: where value score falls vs all others</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Since ratings cluster 4.2-5.0, percentiles make differences interpretable.</t>
         </is>
       </c>
     </row>

--- a/Italian_Ratings.xlsx
+++ b/Italian_Ratings.xlsx
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -569,10 +569,10 @@
         <v>91.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4.482</v>
+        <v>4.451</v>
       </c>
       <c r="N2" t="n">
-        <v>84.3</v>
+        <v>79.7</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -621,10 +621,10 @@
         <v>93.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.296</v>
+        <v>4.224</v>
       </c>
       <c r="N3" t="n">
-        <v>66</v>
+        <v>52.9</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -673,10 +673,10 @@
         <v>78.40000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>4.163</v>
+        <v>4.094</v>
       </c>
       <c r="N4" t="n">
-        <v>47.7</v>
+        <v>32.7</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         <v>90.2</v>
       </c>
       <c r="M5" t="n">
-        <v>4.363</v>
+        <v>4.206</v>
       </c>
       <c r="N5" t="n">
-        <v>72.5</v>
+        <v>51</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
         <v>81</v>
       </c>
       <c r="M6" t="n">
-        <v>4.253</v>
+        <v>4.122</v>
       </c>
       <c r="N6" t="n">
-        <v>58.2</v>
+        <v>39.9</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         <v>38.6</v>
       </c>
       <c r="M7" t="n">
-        <v>4.446</v>
+        <v>4.388</v>
       </c>
       <c r="N7" t="n">
-        <v>81</v>
+        <v>72.5</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1919</v>
+        <v>75</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -881,10 +881,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>2.864</v>
+        <v>3.961</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>17.6</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1976</v>
+        <v>75</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         <v>26.8</v>
       </c>
       <c r="M9" t="n">
-        <v>2.942</v>
+        <v>4.08</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>30.1</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -988,7 +988,7 @@
         <v>4.068</v>
       </c>
       <c r="N10" t="n">
-        <v>34</v>
+        <v>28.1</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1040,7 +1040,7 @@
         <v>4.051</v>
       </c>
       <c r="N11" t="n">
-        <v>31.4</v>
+        <v>24.8</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
         <v>85.59999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>4.079</v>
+        <v>4.165</v>
       </c>
       <c r="N12" t="n">
-        <v>36.6</v>
+        <v>45.1</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1144,7 +1144,7 @@
         <v>4.259</v>
       </c>
       <c r="N13" t="n">
-        <v>60.1</v>
+        <v>59.5</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1193,10 +1193,10 @@
         <v>89.5</v>
       </c>
       <c r="M14" t="n">
-        <v>4.67</v>
+        <v>4.725</v>
       </c>
       <c r="N14" t="n">
-        <v>92.8</v>
+        <v>93.5</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         <v>43.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.86</v>
+        <v>3.915</v>
       </c>
       <c r="N15" t="n">
-        <v>17.6</v>
+        <v>13.1</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         <v>29.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.903</v>
+        <v>3.871</v>
       </c>
       <c r="N16" t="n">
-        <v>20.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -1352,7 +1352,7 @@
         <v>3.933</v>
       </c>
       <c r="N17" t="n">
-        <v>23.5</v>
+        <v>15</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -1404,7 +1404,7 @@
         <v>4.072</v>
       </c>
       <c r="N18" t="n">
-        <v>35.3</v>
+        <v>28.8</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -1456,7 +1456,7 @@
         <v>4.17</v>
       </c>
       <c r="N19" t="n">
-        <v>50.3</v>
+        <v>46.4</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -1508,7 +1508,7 @@
         <v>4.007</v>
       </c>
       <c r="N20" t="n">
-        <v>27.5</v>
+        <v>19.6</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -1560,7 +1560,7 @@
         <v>4.576</v>
       </c>
       <c r="N21" t="n">
-        <v>90.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -1612,7 +1612,7 @@
         <v>4.574</v>
       </c>
       <c r="N22" t="n">
-        <v>90.2</v>
+        <v>88.2</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -1664,7 +1664,7 @@
         <v>4.319</v>
       </c>
       <c r="N23" t="n">
-        <v>68.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -1716,7 +1716,7 @@
         <v>3.947</v>
       </c>
       <c r="N24" t="n">
-        <v>24.2</v>
+        <v>16.3</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -1768,7 +1768,7 @@
         <v>4.856</v>
       </c>
       <c r="N25" t="n">
-        <v>99.3</v>
+        <v>98.7</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -1820,7 +1820,7 @@
         <v>3.919</v>
       </c>
       <c r="N26" t="n">
-        <v>22.2</v>
+        <v>13.7</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -1872,7 +1872,7 @@
         <v>4.93</v>
       </c>
       <c r="N27" t="n">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -1924,7 +1924,7 @@
         <v>4.717</v>
       </c>
       <c r="N28" t="n">
-        <v>95.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -1976,7 +1976,7 @@
         <v>4.39</v>
       </c>
       <c r="N29" t="n">
-        <v>75.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -2028,7 +2028,7 @@
         <v>4.194</v>
       </c>
       <c r="N30" t="n">
-        <v>52.9</v>
+        <v>49</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -2080,7 +2080,7 @@
         <v>3.866</v>
       </c>
       <c r="N31" t="n">
-        <v>18.3</v>
+        <v>8.5</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1908</v>
+        <v>75</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2129,10 +2129,10 @@
         <v>31.4</v>
       </c>
       <c r="M32" t="n">
-        <v>2.965</v>
+        <v>4.097</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>33.3</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -2184,7 +2184,7 @@
         <v>4.338</v>
       </c>
       <c r="N33" t="n">
-        <v>70.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -2236,7 +2236,7 @@
         <v>3.773</v>
       </c>
       <c r="N34" t="n">
-        <v>12.4</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -2288,7 +2288,7 @@
         <v>4.77</v>
       </c>
       <c r="N35" t="n">
-        <v>96.7</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -2340,7 +2340,7 @@
         <v>4.068</v>
       </c>
       <c r="N36" t="n">
-        <v>33.3</v>
+        <v>27.5</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -2392,7 +2392,7 @@
         <v>3.838</v>
       </c>
       <c r="N37" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
@@ -2444,7 +2444,7 @@
         <v>3.988</v>
       </c>
       <c r="N38" t="n">
-        <v>26.1</v>
+        <v>18.3</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -2496,7 +2496,7 @@
         <v>4.12</v>
       </c>
       <c r="N39" t="n">
-        <v>43.8</v>
+        <v>39.2</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>4.164</v>
       </c>
       <c r="N40" t="n">
-        <v>48.4</v>
+        <v>43.8</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -2600,7 +2600,7 @@
         <v>4.532</v>
       </c>
       <c r="N41" t="n">
-        <v>87.59999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -2704,7 +2704,7 @@
         <v>4.665</v>
       </c>
       <c r="N43" t="n">
-        <v>92.2</v>
+        <v>90.2</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -2756,7 +2756,7 @@
         <v>3.882</v>
       </c>
       <c r="N44" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -2808,7 +2808,7 @@
         <v>3.793</v>
       </c>
       <c r="N45" t="n">
-        <v>13.7</v>
+        <v>3.9</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -2860,7 +2860,7 @@
         <v>4.272</v>
       </c>
       <c r="N46" t="n">
-        <v>61.4</v>
+        <v>60.8</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -2906,7 +2906,7 @@
         <v>3.724</v>
       </c>
       <c r="N47" t="n">
-        <v>11.8</v>
+        <v>2</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>4.085</v>
+        <v>4.116</v>
       </c>
       <c r="N48" t="n">
-        <v>37.9</v>
+        <v>37.3</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -3006,7 +3006,7 @@
         <v>4.297</v>
       </c>
       <c r="N49" t="n">
-        <v>66.7</v>
+        <v>64.7</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -3058,7 +3058,7 @@
         <v>4.029</v>
       </c>
       <c r="N50" t="n">
-        <v>28.8</v>
+        <v>20.9</v>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -3110,7 +3110,7 @@
         <v>3.794</v>
       </c>
       <c r="N51" t="n">
-        <v>14.4</v>
+        <v>4.6</v>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -3162,7 +3162,7 @@
         <v>3.911</v>
       </c>
       <c r="N52" t="n">
-        <v>21.6</v>
+        <v>12.4</v>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
         <v>69.90000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>3.98</v>
+        <v>4.037</v>
       </c>
       <c r="N53" t="n">
-        <v>25.5</v>
+        <v>22.2</v>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -3266,7 +3266,7 @@
         <v>3.89</v>
       </c>
       <c r="N54" t="n">
-        <v>19.6</v>
+        <v>11.1</v>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1944</v>
+        <v>130</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3315,10 +3315,10 @@
         <v>73.2</v>
       </c>
       <c r="M55" t="n">
-        <v>3.093</v>
+        <v>4.054</v>
       </c>
       <c r="N55" t="n">
-        <v>7.8</v>
+        <v>25.5</v>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -3370,7 +3370,7 @@
         <v>4.076</v>
       </c>
       <c r="N56" t="n">
-        <v>35.9</v>
+        <v>29.4</v>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -3422,7 +3422,7 @@
         <v>3.829</v>
       </c>
       <c r="N57" t="n">
-        <v>15.7</v>
+        <v>5.9</v>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -3474,7 +3474,7 @@
         <v>4.019</v>
       </c>
       <c r="N58" t="n">
-        <v>28.1</v>
+        <v>20.3</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -3526,7 +3526,7 @@
         <v>4.276</v>
       </c>
       <c r="N59" t="n">
-        <v>62.1</v>
+        <v>61.4</v>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -3578,7 +3578,7 @@
         <v>4.445</v>
       </c>
       <c r="N60" t="n">
-        <v>80.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
@@ -3630,7 +3630,7 @@
         <v>4.123</v>
       </c>
       <c r="N61" t="n">
-        <v>44.4</v>
+        <v>40.5</v>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
@@ -3682,7 +3682,7 @@
         <v>4.46</v>
       </c>
       <c r="N62" t="n">
-        <v>83</v>
+        <v>81.7</v>
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
@@ -3734,7 +3734,7 @@
         <v>4.564</v>
       </c>
       <c r="N63" t="n">
-        <v>89.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -3786,7 +3786,7 @@
         <v>4.535</v>
       </c>
       <c r="N64" t="n">
-        <v>88.2</v>
+        <v>86.3</v>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1896</v>
+        <v>130</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
         <v>68</v>
       </c>
       <c r="M65" t="n">
-        <v>3.082</v>
+        <v>4.029</v>
       </c>
       <c r="N65" t="n">
-        <v>7.2</v>
+        <v>21.6</v>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1981</v>
+        <v>130</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3887,10 +3887,10 @@
         <v>3.3</v>
       </c>
       <c r="M66" t="n">
-        <v>2.744</v>
+        <v>3.603</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -3942,7 +3942,7 @@
         <v>4.063</v>
       </c>
       <c r="N67" t="n">
-        <v>32.7</v>
+        <v>26.8</v>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -3994,7 +3994,7 @@
         <v>4.374</v>
       </c>
       <c r="N68" t="n">
-        <v>73.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -4046,7 +4046,7 @@
         <v>3.891</v>
       </c>
       <c r="N69" t="n">
-        <v>20.3</v>
+        <v>11.8</v>
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -4098,7 +4098,7 @@
         <v>3.83</v>
       </c>
       <c r="N70" t="n">
-        <v>16.3</v>
+        <v>6.5</v>
       </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -4150,7 +4150,7 @@
         <v>4.043</v>
       </c>
       <c r="N71" t="n">
-        <v>30.1</v>
+        <v>23.5</v>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -4254,7 +4254,7 @@
         <v>4.498</v>
       </c>
       <c r="N73" t="n">
-        <v>85.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4303,10 +4303,10 @@
         <v>50.3</v>
       </c>
       <c r="M74" t="n">
-        <v>4.071</v>
+        <v>3.945</v>
       </c>
       <c r="N74" t="n">
-        <v>34.6</v>
+        <v>15.7</v>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4355,10 +4355,10 @@
         <v>52.9</v>
       </c>
       <c r="M75" t="n">
-        <v>4.124</v>
+        <v>3.952</v>
       </c>
       <c r="N75" t="n">
-        <v>45.8</v>
+        <v>17</v>
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4407,10 +4407,10 @@
         <v>26.1</v>
       </c>
       <c r="M76" t="n">
-        <v>3.958</v>
+        <v>3.856</v>
       </c>
       <c r="N76" t="n">
-        <v>24.8</v>
+        <v>7.8</v>
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -4462,7 +4462,7 @@
         <v>4.169</v>
       </c>
       <c r="N77" t="n">
-        <v>49.7</v>
+        <v>45.8</v>
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -4514,7 +4514,7 @@
         <v>4.346</v>
       </c>
       <c r="N78" t="n">
-        <v>71.2</v>
+        <v>69.3</v>
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -4566,7 +4566,7 @@
         <v>4.104</v>
       </c>
       <c r="N79" t="n">
-        <v>40.5</v>
+        <v>34.6</v>
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
@@ -4618,7 +4618,7 @@
         <v>4.285</v>
       </c>
       <c r="N80" t="n">
-        <v>64.09999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
@@ -4670,7 +4670,7 @@
         <v>4.409</v>
       </c>
       <c r="N81" t="n">
-        <v>77.8</v>
+        <v>75.8</v>
       </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -4719,10 +4719,10 @@
         <v>62.1</v>
       </c>
       <c r="M82" t="n">
-        <v>4.288</v>
+        <v>4.227</v>
       </c>
       <c r="N82" t="n">
-        <v>64.7</v>
+        <v>54.2</v>
       </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
@@ -4774,7 +4774,7 @@
         <v>4.779</v>
       </c>
       <c r="N83" t="n">
-        <v>97.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
@@ -4826,7 +4826,7 @@
         <v>4.175</v>
       </c>
       <c r="N84" t="n">
-        <v>51</v>
+        <v>47.1</v>
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
@@ -4878,7 +4878,7 @@
         <v>4.483</v>
       </c>
       <c r="N85" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
@@ -4930,7 +4930,7 @@
         <v>4.432</v>
       </c>
       <c r="N86" t="n">
-        <v>79.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
@@ -4982,7 +4982,7 @@
         <v>4.13</v>
       </c>
       <c r="N87" t="n">
-        <v>47.1</v>
+        <v>42.5</v>
       </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1904</v>
+        <v>18</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5031,10 +5031,10 @@
         <v>41.2</v>
       </c>
       <c r="M88" t="n">
-        <v>2.99</v>
+        <v>4.766</v>
       </c>
       <c r="N88" t="n">
-        <v>3.9</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
@@ -5086,7 +5086,7 @@
         <v>4.11</v>
       </c>
       <c r="N89" t="n">
-        <v>42.5</v>
+        <v>36.6</v>
       </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
@@ -5190,7 +5190,7 @@
         <v>4.293</v>
       </c>
       <c r="N91" t="n">
-        <v>65.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
@@ -5242,7 +5242,7 @@
         <v>4.841</v>
       </c>
       <c r="N92" t="n">
-        <v>98</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -5294,7 +5294,7 @@
         <v>4.456</v>
       </c>
       <c r="N93" t="n">
-        <v>81.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -5346,7 +5346,7 @@
         <v>4.11</v>
       </c>
       <c r="N94" t="n">
-        <v>41.8</v>
+        <v>35.9</v>
       </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -5398,7 +5398,7 @@
         <v>4.463</v>
       </c>
       <c r="N95" t="n">
-        <v>83.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1907</v>
+        <v>130</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5447,10 +5447,10 @@
         <v>28.8</v>
       </c>
       <c r="M96" t="n">
-        <v>2.958</v>
+        <v>3.869</v>
       </c>
       <c r="N96" t="n">
-        <v>2.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1939</v>
+        <v>40</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
         <v>92.8</v>
       </c>
       <c r="M97" t="n">
-        <v>3.222</v>
+        <v>4.749</v>
       </c>
       <c r="N97" t="n">
-        <v>9.199999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -5554,7 +5554,7 @@
         <v>4.039</v>
       </c>
       <c r="N98" t="n">
-        <v>29.4</v>
+        <v>22.9</v>
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1991</v>
+        <v>75</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -5603,10 +5603,10 @@
         <v>86.90000000000001</v>
       </c>
       <c r="M99" t="n">
-        <v>3.182</v>
+        <v>4.417</v>
       </c>
       <c r="N99" t="n">
-        <v>8.5</v>
+        <v>76.5</v>
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1964</v>
+        <v>75</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -5655,10 +5655,10 @@
         <v>59.5</v>
       </c>
       <c r="M100" t="n">
-        <v>3.036</v>
+        <v>4.208</v>
       </c>
       <c r="N100" t="n">
-        <v>5.9</v>
+        <v>51.6</v>
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1932</v>
+        <v>40</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -5707,10 +5707,10 @@
         <v>6.5</v>
       </c>
       <c r="M101" t="n">
-        <v>2.796</v>
+        <v>4.12</v>
       </c>
       <c r="N101" t="n">
-        <v>0.7</v>
+        <v>38.6</v>
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
@@ -5762,7 +5762,7 @@
         <v>4.256</v>
       </c>
       <c r="N102" t="n">
-        <v>59.5</v>
+        <v>58.8</v>
       </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
@@ -5814,7 +5814,7 @@
         <v>4.459</v>
       </c>
       <c r="N103" t="n">
-        <v>82.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -5866,7 +5866,7 @@
         <v>3.589</v>
       </c>
       <c r="N104" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1964</v>
+        <v>75</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -5915,10 +5915,10 @@
         <v>60.1</v>
       </c>
       <c r="M105" t="n">
-        <v>3.047</v>
+        <v>4.224</v>
       </c>
       <c r="N105" t="n">
-        <v>6.5</v>
+        <v>52.3</v>
       </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
@@ -5970,7 +5970,7 @@
         <v>4.164</v>
       </c>
       <c r="N106" t="n">
-        <v>49</v>
+        <v>44.4</v>
       </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -6022,7 +6022,7 @@
         <v>4.306</v>
       </c>
       <c r="N107" t="n">
-        <v>67.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -6074,7 +6074,7 @@
         <v>3.782</v>
       </c>
       <c r="N108" t="n">
-        <v>13.1</v>
+        <v>3.3</v>
       </c>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
@@ -6126,7 +6126,7 @@
         <v>4.101</v>
       </c>
       <c r="N109" t="n">
-        <v>39.9</v>
+        <v>34</v>
       </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
@@ -6230,7 +6230,7 @@
         <v>4.125</v>
       </c>
       <c r="N111" t="n">
-        <v>46.4</v>
+        <v>41.8</v>
       </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
@@ -6282,7 +6282,7 @@
         <v>3.807</v>
       </c>
       <c r="N112" t="n">
-        <v>15</v>
+        <v>5.2</v>
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
@@ -6334,7 +6334,7 @@
         <v>4.715</v>
       </c>
       <c r="N113" t="n">
-        <v>94.8</v>
+        <v>92.2</v>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
@@ -6386,7 +6386,7 @@
         <v>4.082</v>
       </c>
       <c r="N114" t="n">
-        <v>37.3</v>
+        <v>30.7</v>
       </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
@@ -6438,7 +6438,7 @@
         <v>4.204</v>
       </c>
       <c r="N115" t="n">
-        <v>53.6</v>
+        <v>49.7</v>
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
@@ -6490,7 +6490,7 @@
         <v>4.278</v>
       </c>
       <c r="N116" t="n">
-        <v>62.7</v>
+        <v>62.1</v>
       </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1968</v>
+        <v>75</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -6539,10 +6539,10 @@
         <v>58.8</v>
       </c>
       <c r="M117" t="n">
-        <v>3.033</v>
+        <v>4.205</v>
       </c>
       <c r="N117" t="n">
-        <v>5.2</v>
+        <v>50.3</v>
       </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
@@ -6594,7 +6594,7 @@
         <v>4.119</v>
       </c>
       <c r="N118" t="n">
-        <v>43.1</v>
+        <v>37.9</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
@@ -6646,7 +6646,7 @@
         <v>4.368</v>
       </c>
       <c r="N119" t="n">
-        <v>73.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
@@ -6698,7 +6698,7 @@
         <v>4.52</v>
       </c>
       <c r="N120" t="n">
-        <v>86.3</v>
+        <v>84.3</v>
       </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
@@ -6750,7 +6750,7 @@
         <v>4.743</v>
       </c>
       <c r="N121" t="n">
-        <v>96.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
@@ -6802,7 +6802,7 @@
         <v>4.578</v>
       </c>
       <c r="N122" t="n">
-        <v>91.5</v>
+        <v>89.5</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
@@ -6854,7 +6854,7 @@
         <v>4.404</v>
       </c>
       <c r="N123" t="n">
-        <v>76.5</v>
+        <v>74.5</v>
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
@@ -6906,7 +6906,7 @@
         <v>4.28</v>
       </c>
       <c r="N124" t="n">
-        <v>63.4</v>
+        <v>62.7</v>
       </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
@@ -6958,7 +6958,7 @@
         <v>4.409</v>
       </c>
       <c r="N125" t="n">
-        <v>77.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
@@ -7010,7 +7010,7 @@
         <v>3.931</v>
       </c>
       <c r="N126" t="n">
-        <v>22.9</v>
+        <v>14.4</v>
       </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -7062,7 +7062,7 @@
         <v>4.38</v>
       </c>
       <c r="N127" t="n">
-        <v>74.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
@@ -7114,7 +7114,7 @@
         <v>4.227</v>
       </c>
       <c r="N128" t="n">
-        <v>54.2</v>
+        <v>53.6</v>
       </c>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
@@ -7166,7 +7166,7 @@
         <v>4.267</v>
       </c>
       <c r="N129" t="n">
-        <v>60.8</v>
+        <v>60.1</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -7218,7 +7218,7 @@
         <v>4.436</v>
       </c>
       <c r="N130" t="n">
-        <v>79.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -7270,7 +7270,7 @@
         <v>4.06</v>
       </c>
       <c r="N131" t="n">
-        <v>32</v>
+        <v>26.1</v>
       </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
@@ -7322,7 +7322,7 @@
         <v>4.123</v>
       </c>
       <c r="N132" t="n">
-        <v>45.1</v>
+        <v>41.2</v>
       </c>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
@@ -7374,7 +7374,7 @@
         <v>4.092</v>
       </c>
       <c r="N133" t="n">
-        <v>39.2</v>
+        <v>32</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
@@ -7426,7 +7426,7 @@
         <v>4.712</v>
       </c>
       <c r="N134" t="n">
-        <v>94.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -7478,7 +7478,7 @@
         <v>4.547</v>
       </c>
       <c r="N135" t="n">
-        <v>88.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -7530,7 +7530,7 @@
         <v>4.679</v>
       </c>
       <c r="N136" t="n">
-        <v>93.5</v>
+        <v>90.8</v>
       </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -7582,7 +7582,7 @@
         <v>4.529</v>
       </c>
       <c r="N137" t="n">
-        <v>86.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
@@ -7634,7 +7634,7 @@
         <v>4.335</v>
       </c>
       <c r="N138" t="n">
-        <v>69.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -7686,7 +7686,7 @@
         <v>4.109</v>
       </c>
       <c r="N139" t="n">
-        <v>41.2</v>
+        <v>35.3</v>
       </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1962</v>
+        <v>75</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -7735,10 +7735,10 @@
         <v>46.4</v>
       </c>
       <c r="M140" t="n">
-        <v>2.991</v>
+        <v>4.145</v>
       </c>
       <c r="N140" t="n">
-        <v>4.6</v>
+        <v>43.1</v>
       </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -7790,7 +7790,7 @@
         <v>4.088</v>
       </c>
       <c r="N141" t="n">
-        <v>38.6</v>
+        <v>31.4</v>
       </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -7842,7 +7842,7 @@
         <v>4.183</v>
       </c>
       <c r="N142" t="n">
-        <v>51.6</v>
+        <v>47.7</v>
       </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
@@ -7894,7 +7894,7 @@
         <v>4.324</v>
       </c>
       <c r="N143" t="n">
-        <v>69.3</v>
+        <v>67.3</v>
       </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
@@ -7946,7 +7946,7 @@
         <v>4.389</v>
       </c>
       <c r="N144" t="n">
-        <v>75.2</v>
+        <v>73.2</v>
       </c>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
@@ -7998,7 +7998,7 @@
         <v>4.844</v>
       </c>
       <c r="N145" t="n">
-        <v>98.7</v>
+        <v>98</v>
       </c>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
@@ -8050,7 +8050,7 @@
         <v>3.997</v>
       </c>
       <c r="N146" t="n">
-        <v>26.8</v>
+        <v>19</v>
       </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -8102,7 +8102,7 @@
         <v>4.42</v>
       </c>
       <c r="N147" t="n">
-        <v>78.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
@@ -8154,7 +8154,7 @@
         <v>4.256</v>
       </c>
       <c r="N148" t="n">
-        <v>58.8</v>
+        <v>58.2</v>
       </c>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
@@ -8206,7 +8206,7 @@
         <v>4.045</v>
       </c>
       <c r="N149" t="n">
-        <v>30.7</v>
+        <v>24.2</v>
       </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
@@ -8310,7 +8310,7 @@
         <v>4.19</v>
       </c>
       <c r="N151" t="n">
-        <v>52.3</v>
+        <v>48.4</v>
       </c>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1959</v>
+        <v>18</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -8359,10 +8359,10 @@
         <v>94.09999999999999</v>
       </c>
       <c r="M152" t="n">
-        <v>3.225</v>
+        <v>5.155</v>
       </c>
       <c r="N152" t="n">
-        <v>9.800000000000001</v>
+        <v>100</v>
       </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
@@ -8414,7 +8414,7 @@
         <v>3.619</v>
       </c>
       <c r="N153" t="n">
-        <v>11.1</v>
+        <v>1.3</v>
       </c>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
@@ -8466,7 +8466,7 @@
         <v>4.311</v>
       </c>
       <c r="N154" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
@@ -8518,7 +8518,7 @@
         <v>4.362</v>
       </c>
       <c r="N155" t="n">
-        <v>71.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">

--- a/Italian_Ratings.xlsx
+++ b/Italian_Ratings.xlsx
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -569,10 +569,10 @@
         <v>91.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4.451</v>
+        <v>4.482</v>
       </c>
       <c r="N2" t="n">
-        <v>79.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -621,10 +621,10 @@
         <v>93.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.224</v>
+        <v>4.296</v>
       </c>
       <c r="N3" t="n">
-        <v>52.9</v>
+        <v>63.4</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -673,10 +673,10 @@
         <v>78.40000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>4.094</v>
+        <v>4.163</v>
       </c>
       <c r="N4" t="n">
-        <v>32.7</v>
+        <v>43.1</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         <v>90.2</v>
       </c>
       <c r="M5" t="n">
-        <v>4.206</v>
+        <v>4.363</v>
       </c>
       <c r="N5" t="n">
-        <v>51</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
         <v>81</v>
       </c>
       <c r="M6" t="n">
-        <v>4.122</v>
+        <v>4.253</v>
       </c>
       <c r="N6" t="n">
-        <v>39.9</v>
+        <v>55.6</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         <v>38.6</v>
       </c>
       <c r="M7" t="n">
-        <v>4.388</v>
+        <v>4.446</v>
       </c>
       <c r="N7" t="n">
-        <v>72.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -884,7 +884,7 @@
         <v>3.961</v>
       </c>
       <c r="N8" t="n">
-        <v>17.6</v>
+        <v>16.3</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -988,7 +988,7 @@
         <v>4.068</v>
       </c>
       <c r="N10" t="n">
-        <v>28.1</v>
+        <v>26.8</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1040,7 +1040,7 @@
         <v>4.051</v>
       </c>
       <c r="N11" t="n">
-        <v>24.8</v>
+        <v>23.5</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
         <v>85.59999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>4.165</v>
+        <v>4.079</v>
       </c>
       <c r="N12" t="n">
-        <v>45.1</v>
+        <v>29.4</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1144,7 +1144,7 @@
         <v>4.259</v>
       </c>
       <c r="N13" t="n">
-        <v>59.5</v>
+        <v>57.5</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1193,10 +1193,10 @@
         <v>89.5</v>
       </c>
       <c r="M14" t="n">
-        <v>4.725</v>
+        <v>4.67</v>
       </c>
       <c r="N14" t="n">
-        <v>93.5</v>
+        <v>90.8</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         <v>43.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.915</v>
+        <v>3.86</v>
       </c>
       <c r="N15" t="n">
-        <v>13.1</v>
+        <v>7.8</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         <v>29.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.871</v>
+        <v>3.903</v>
       </c>
       <c r="N16" t="n">
-        <v>9.800000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -1352,7 +1352,7 @@
         <v>3.933</v>
       </c>
       <c r="N17" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -1404,7 +1404,7 @@
         <v>4.072</v>
       </c>
       <c r="N18" t="n">
-        <v>28.8</v>
+        <v>28.1</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -1456,7 +1456,7 @@
         <v>4.17</v>
       </c>
       <c r="N19" t="n">
-        <v>46.4</v>
+        <v>45.8</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -1508,7 +1508,7 @@
         <v>4.007</v>
       </c>
       <c r="N20" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -1664,7 +1664,7 @@
         <v>4.319</v>
       </c>
       <c r="N23" t="n">
-        <v>66.7</v>
+        <v>66</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -1716,7 +1716,7 @@
         <v>3.947</v>
       </c>
       <c r="N24" t="n">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -1820,7 +1820,7 @@
         <v>3.919</v>
       </c>
       <c r="N26" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -1924,7 +1924,7 @@
         <v>4.717</v>
       </c>
       <c r="N28" t="n">
-        <v>92.8</v>
+        <v>93.5</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -1976,7 +1976,7 @@
         <v>4.39</v>
       </c>
       <c r="N29" t="n">
-        <v>73.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -2028,7 +2028,7 @@
         <v>4.194</v>
       </c>
       <c r="N30" t="n">
-        <v>49</v>
+        <v>48.4</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -2184,7 +2184,7 @@
         <v>4.338</v>
       </c>
       <c r="N33" t="n">
-        <v>68.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -2340,7 +2340,7 @@
         <v>4.068</v>
       </c>
       <c r="N36" t="n">
-        <v>27.5</v>
+        <v>26.1</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -2444,7 +2444,7 @@
         <v>3.988</v>
       </c>
       <c r="N38" t="n">
-        <v>18.3</v>
+        <v>17.6</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -2496,7 +2496,7 @@
         <v>4.12</v>
       </c>
       <c r="N39" t="n">
-        <v>39.2</v>
+        <v>38.6</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -2652,7 +2652,7 @@
         <v>4.246</v>
       </c>
       <c r="N42" t="n">
-        <v>56.9</v>
+        <v>54.2</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -2756,7 +2756,7 @@
         <v>3.882</v>
       </c>
       <c r="N44" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -2860,7 +2860,7 @@
         <v>4.272</v>
       </c>
       <c r="N46" t="n">
-        <v>60.8</v>
+        <v>58.8</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>4.116</v>
+        <v>4.085</v>
       </c>
       <c r="N48" t="n">
-        <v>37.3</v>
+        <v>31.4</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -3006,7 +3006,7 @@
         <v>4.297</v>
       </c>
       <c r="N49" t="n">
-        <v>64.7</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -3058,7 +3058,7 @@
         <v>4.029</v>
       </c>
       <c r="N50" t="n">
-        <v>20.9</v>
+        <v>20.3</v>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
         <v>69.90000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>4.037</v>
+        <v>3.98</v>
       </c>
       <c r="N53" t="n">
-        <v>22.2</v>
+        <v>17</v>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -3266,7 +3266,7 @@
         <v>3.89</v>
       </c>
       <c r="N54" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
@@ -3318,7 +3318,7 @@
         <v>4.054</v>
       </c>
       <c r="N55" t="n">
-        <v>25.5</v>
+        <v>24.2</v>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -3370,7 +3370,7 @@
         <v>4.076</v>
       </c>
       <c r="N56" t="n">
-        <v>29.4</v>
+        <v>28.8</v>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -3474,7 +3474,7 @@
         <v>4.019</v>
       </c>
       <c r="N58" t="n">
-        <v>20.3</v>
+        <v>19.6</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -3526,7 +3526,7 @@
         <v>4.276</v>
       </c>
       <c r="N59" t="n">
-        <v>61.4</v>
+        <v>59.5</v>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -3578,7 +3578,7 @@
         <v>4.445</v>
       </c>
       <c r="N60" t="n">
-        <v>79.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
@@ -3630,7 +3630,7 @@
         <v>4.123</v>
       </c>
       <c r="N61" t="n">
-        <v>40.5</v>
+        <v>39.2</v>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
@@ -3682,7 +3682,7 @@
         <v>4.46</v>
       </c>
       <c r="N62" t="n">
-        <v>81.7</v>
+        <v>81</v>
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
@@ -3838,7 +3838,7 @@
         <v>4.029</v>
       </c>
       <c r="N65" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -3942,7 +3942,7 @@
         <v>4.063</v>
       </c>
       <c r="N67" t="n">
-        <v>26.8</v>
+        <v>25.5</v>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -4046,7 +4046,7 @@
         <v>3.891</v>
       </c>
       <c r="N69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -4150,7 +4150,7 @@
         <v>4.043</v>
       </c>
       <c r="N71" t="n">
-        <v>23.5</v>
+        <v>22.2</v>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -4202,7 +4202,7 @@
         <v>4.235</v>
       </c>
       <c r="N72" t="n">
-        <v>54.9</v>
+        <v>52.3</v>
       </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4303,10 +4303,10 @@
         <v>50.3</v>
       </c>
       <c r="M74" t="n">
-        <v>3.945</v>
+        <v>4.071</v>
       </c>
       <c r="N74" t="n">
-        <v>15.7</v>
+        <v>27.5</v>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4355,10 +4355,10 @@
         <v>52.9</v>
       </c>
       <c r="M75" t="n">
-        <v>3.952</v>
+        <v>4.124</v>
       </c>
       <c r="N75" t="n">
-        <v>17</v>
+        <v>40.5</v>
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4407,10 +4407,10 @@
         <v>26.1</v>
       </c>
       <c r="M76" t="n">
-        <v>3.856</v>
+        <v>3.958</v>
       </c>
       <c r="N76" t="n">
-        <v>7.8</v>
+        <v>15.7</v>
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -4462,7 +4462,7 @@
         <v>4.169</v>
       </c>
       <c r="N77" t="n">
-        <v>45.8</v>
+        <v>45.1</v>
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -4514,7 +4514,7 @@
         <v>4.346</v>
       </c>
       <c r="N78" t="n">
-        <v>69.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -4618,7 +4618,7 @@
         <v>4.285</v>
       </c>
       <c r="N80" t="n">
-        <v>63.4</v>
+        <v>61.4</v>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
@@ -4670,7 +4670,7 @@
         <v>4.409</v>
       </c>
       <c r="N81" t="n">
-        <v>75.8</v>
+        <v>75.2</v>
       </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -4719,10 +4719,10 @@
         <v>62.1</v>
       </c>
       <c r="M82" t="n">
-        <v>4.227</v>
+        <v>4.288</v>
       </c>
       <c r="N82" t="n">
-        <v>54.2</v>
+        <v>62.1</v>
       </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
@@ -4826,7 +4826,7 @@
         <v>4.175</v>
       </c>
       <c r="N84" t="n">
-        <v>47.1</v>
+        <v>46.4</v>
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
@@ -4930,7 +4930,7 @@
         <v>4.432</v>
       </c>
       <c r="N86" t="n">
-        <v>77.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
@@ -4982,7 +4982,7 @@
         <v>4.13</v>
       </c>
       <c r="N87" t="n">
-        <v>42.5</v>
+        <v>41.8</v>
       </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
@@ -5138,7 +5138,7 @@
         <v>4.251</v>
       </c>
       <c r="N90" t="n">
-        <v>57.5</v>
+        <v>54.9</v>
       </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
@@ -5190,7 +5190,7 @@
         <v>4.293</v>
       </c>
       <c r="N91" t="n">
-        <v>64.09999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
@@ -5294,7 +5294,7 @@
         <v>4.456</v>
       </c>
       <c r="N93" t="n">
-        <v>80.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -5398,7 +5398,7 @@
         <v>4.463</v>
       </c>
       <c r="N95" t="n">
-        <v>82.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -5554,7 +5554,7 @@
         <v>4.039</v>
       </c>
       <c r="N98" t="n">
-        <v>22.9</v>
+        <v>21.6</v>
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
@@ -5606,7 +5606,7 @@
         <v>4.417</v>
       </c>
       <c r="N99" t="n">
-        <v>76.5</v>
+        <v>75.8</v>
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
@@ -5658,7 +5658,7 @@
         <v>4.208</v>
       </c>
       <c r="N100" t="n">
-        <v>51.6</v>
+        <v>50.3</v>
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -5710,7 +5710,7 @@
         <v>4.12</v>
       </c>
       <c r="N101" t="n">
-        <v>38.6</v>
+        <v>37.9</v>
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
@@ -5762,7 +5762,7 @@
         <v>4.256</v>
       </c>
       <c r="N102" t="n">
-        <v>58.8</v>
+        <v>56.9</v>
       </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
@@ -5814,7 +5814,7 @@
         <v>4.459</v>
       </c>
       <c r="N103" t="n">
-        <v>81</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -5918,7 +5918,7 @@
         <v>4.224</v>
       </c>
       <c r="N105" t="n">
-        <v>52.3</v>
+        <v>51</v>
       </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
@@ -6022,7 +6022,7 @@
         <v>4.306</v>
       </c>
       <c r="N107" t="n">
-        <v>65.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -6178,7 +6178,7 @@
         <v>4.244</v>
       </c>
       <c r="N110" t="n">
-        <v>56.2</v>
+        <v>53.6</v>
       </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
@@ -6230,7 +6230,7 @@
         <v>4.125</v>
       </c>
       <c r="N111" t="n">
-        <v>41.8</v>
+        <v>41.2</v>
       </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
@@ -6334,7 +6334,7 @@
         <v>4.715</v>
       </c>
       <c r="N113" t="n">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
@@ -6438,7 +6438,7 @@
         <v>4.204</v>
       </c>
       <c r="N115" t="n">
-        <v>49.7</v>
+        <v>49</v>
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
@@ -6490,7 +6490,7 @@
         <v>4.278</v>
       </c>
       <c r="N116" t="n">
-        <v>62.1</v>
+        <v>60.1</v>
       </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
@@ -6542,7 +6542,7 @@
         <v>4.205</v>
       </c>
       <c r="N117" t="n">
-        <v>50.3</v>
+        <v>49.7</v>
       </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
@@ -6594,7 +6594,7 @@
         <v>4.119</v>
       </c>
       <c r="N118" t="n">
-        <v>37.9</v>
+        <v>37.3</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
@@ -6854,7 +6854,7 @@
         <v>4.404</v>
       </c>
       <c r="N123" t="n">
-        <v>74.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
@@ -6906,7 +6906,7 @@
         <v>4.28</v>
       </c>
       <c r="N124" t="n">
-        <v>62.7</v>
+        <v>60.8</v>
       </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
@@ -6958,7 +6958,7 @@
         <v>4.409</v>
       </c>
       <c r="N125" t="n">
-        <v>75.2</v>
+        <v>74.5</v>
       </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
@@ -7010,7 +7010,7 @@
         <v>3.931</v>
       </c>
       <c r="N126" t="n">
-        <v>14.4</v>
+        <v>13.7</v>
       </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -7114,7 +7114,7 @@
         <v>4.227</v>
       </c>
       <c r="N128" t="n">
-        <v>53.6</v>
+        <v>51.6</v>
       </c>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
@@ -7166,7 +7166,7 @@
         <v>4.267</v>
       </c>
       <c r="N129" t="n">
-        <v>60.1</v>
+        <v>58.2</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -7218,7 +7218,7 @@
         <v>4.436</v>
       </c>
       <c r="N130" t="n">
-        <v>78.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -7270,7 +7270,7 @@
         <v>4.06</v>
       </c>
       <c r="N131" t="n">
-        <v>26.1</v>
+        <v>24.8</v>
       </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
@@ -7322,7 +7322,7 @@
         <v>4.123</v>
       </c>
       <c r="N132" t="n">
-        <v>41.2</v>
+        <v>39.9</v>
       </c>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
@@ -7374,7 +7374,7 @@
         <v>4.092</v>
       </c>
       <c r="N133" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
@@ -7426,7 +7426,7 @@
         <v>4.712</v>
       </c>
       <c r="N134" t="n">
-        <v>91.5</v>
+        <v>92.2</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -7530,7 +7530,7 @@
         <v>4.679</v>
       </c>
       <c r="N136" t="n">
-        <v>90.8</v>
+        <v>91.5</v>
       </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -7634,7 +7634,7 @@
         <v>4.335</v>
       </c>
       <c r="N138" t="n">
-        <v>68</v>
+        <v>67.3</v>
       </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -7738,7 +7738,7 @@
         <v>4.145</v>
       </c>
       <c r="N140" t="n">
-        <v>43.1</v>
+        <v>42.5</v>
       </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -7790,7 +7790,7 @@
         <v>4.088</v>
       </c>
       <c r="N141" t="n">
-        <v>31.4</v>
+        <v>32</v>
       </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -7842,7 +7842,7 @@
         <v>4.183</v>
       </c>
       <c r="N142" t="n">
-        <v>47.7</v>
+        <v>47.1</v>
       </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
@@ -7894,7 +7894,7 @@
         <v>4.324</v>
       </c>
       <c r="N143" t="n">
-        <v>67.3</v>
+        <v>66.7</v>
       </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
@@ -7946,7 +7946,7 @@
         <v>4.389</v>
       </c>
       <c r="N144" t="n">
-        <v>73.2</v>
+        <v>72.5</v>
       </c>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
@@ -8050,7 +8050,7 @@
         <v>3.997</v>
       </c>
       <c r="N146" t="n">
-        <v>19</v>
+        <v>18.3</v>
       </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -8102,7 +8102,7 @@
         <v>4.42</v>
       </c>
       <c r="N147" t="n">
-        <v>77.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
@@ -8154,7 +8154,7 @@
         <v>4.256</v>
       </c>
       <c r="N148" t="n">
-        <v>58.2</v>
+        <v>56.2</v>
       </c>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
@@ -8206,7 +8206,7 @@
         <v>4.045</v>
       </c>
       <c r="N149" t="n">
-        <v>24.2</v>
+        <v>22.9</v>
       </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
@@ -8258,7 +8258,7 @@
         <v>4.238</v>
       </c>
       <c r="N150" t="n">
-        <v>55.6</v>
+        <v>52.9</v>
       </c>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
@@ -8310,7 +8310,7 @@
         <v>4.19</v>
       </c>
       <c r="N151" t="n">
-        <v>48.4</v>
+        <v>47.7</v>
       </c>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -8466,7 +8466,7 @@
         <v>4.311</v>
       </c>
       <c r="N154" t="n">
-        <v>66</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
@@ -8518,7 +8518,7 @@
         <v>4.362</v>
       </c>
       <c r="N155" t="n">
-        <v>69.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">

--- a/Italian_Ratings.xlsx
+++ b/Italian_Ratings.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -560,7 +560,7 @@
         <v>4.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3254</v>
+        <v>3312</v>
       </c>
       <c r="K2" t="n">
         <v>4.325</v>
@@ -572,7 +572,7 @@
         <v>4.482</v>
       </c>
       <c r="N2" t="n">
-        <v>82.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -609,22 +609,22 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>1778</v>
+        <v>1829</v>
       </c>
       <c r="K3" t="n">
-        <v>4.337</v>
+        <v>4.302</v>
       </c>
       <c r="L3" t="n">
-        <v>93.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>4.296</v>
+        <v>4.261</v>
       </c>
       <c r="N3" t="n">
-        <v>63.4</v>
+        <v>58.2</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -664,19 +664,19 @@
         <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>402</v>
+        <v>440</v>
       </c>
       <c r="K4" t="n">
-        <v>4.203</v>
+        <v>4.205</v>
       </c>
       <c r="L4" t="n">
         <v>78.40000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>4.163</v>
+        <v>4.165</v>
       </c>
       <c r="N4" t="n">
-        <v>43.1</v>
+        <v>45.1</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -716,7 +716,7 @@
         <v>4.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2582</v>
+        <v>2631</v>
       </c>
       <c r="K5" t="n">
         <v>4.318</v>
@@ -725,10 +725,10 @@
         <v>90.2</v>
       </c>
       <c r="M5" t="n">
-        <v>4.363</v>
+        <v>4.364</v>
       </c>
       <c r="N5" t="n">
-        <v>69.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -768,16 +768,16 @@
         <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1050</v>
+        <v>1082</v>
       </c>
       <c r="K6" t="n">
-        <v>4.231</v>
+        <v>4.232</v>
       </c>
       <c r="L6" t="n">
-        <v>81</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>4.253</v>
+        <v>4.254</v>
       </c>
       <c r="N6" t="n">
         <v>55.6</v>
@@ -797,7 +797,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -820,19 +820,19 @@
         <v>4.1</v>
       </c>
       <c r="J7" t="n">
-        <v>942</v>
+        <v>969</v>
       </c>
       <c r="K7" t="n">
-        <v>4.003</v>
+        <v>4.004</v>
       </c>
       <c r="L7" t="n">
-        <v>38.6</v>
+        <v>35.3</v>
       </c>
       <c r="M7" t="n">
-        <v>4.446</v>
+        <v>4.447</v>
       </c>
       <c r="N7" t="n">
-        <v>79.09999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -872,19 +872,19 @@
         <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K8" t="n">
-        <v>3.848</v>
+        <v>3.849</v>
       </c>
       <c r="L8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>3.961</v>
       </c>
       <c r="N8" t="n">
-        <v>16.3</v>
+        <v>15.7</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -924,19 +924,19 @@
         <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K9" t="n">
         <v>3.964</v>
       </c>
       <c r="L9" t="n">
-        <v>26.8</v>
+        <v>26.1</v>
       </c>
       <c r="M9" t="n">
         <v>4.08</v>
       </c>
       <c r="N9" t="n">
-        <v>30.1</v>
+        <v>32.7</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -976,19 +976,19 @@
         <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1798</v>
+        <v>1805</v>
       </c>
       <c r="K10" t="n">
         <v>4.177</v>
       </c>
       <c r="L10" t="n">
-        <v>76.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>4.068</v>
       </c>
       <c r="N10" t="n">
-        <v>26.8</v>
+        <v>28.8</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1025,27 +1025,27 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1826</v>
+        <v>1256</v>
       </c>
       <c r="K11" t="n">
-        <v>3.936</v>
+        <v>3.896</v>
       </c>
       <c r="L11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.009</v>
+      </c>
+      <c r="N11" t="n">
         <v>21.6</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.051</v>
-      </c>
-      <c r="N11" t="n">
-        <v>23.5</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nami Nori West Village</t>
+          <t>Lupa</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1080,19 +1080,19 @@
         <v>4.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2611</v>
+        <v>2671</v>
       </c>
       <c r="K12" t="n">
         <v>4.276</v>
       </c>
       <c r="L12" t="n">
-        <v>85.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4.079</v>
+        <v>4.08</v>
       </c>
       <c r="N12" t="n">
-        <v>29.4</v>
+        <v>32</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1132,13 +1132,13 @@
         <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1660</v>
+        <v>1684</v>
       </c>
       <c r="K13" t="n">
         <v>4.138</v>
       </c>
       <c r="L13" t="n">
-        <v>69.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>4.259</v>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1184,7 +1184,7 @@
         <v>4.6</v>
       </c>
       <c r="J14" t="n">
-        <v>7099</v>
+        <v>7414</v>
       </c>
       <c r="K14" t="n">
         <v>4.312</v>
@@ -1196,7 +1196,7 @@
         <v>4.67</v>
       </c>
       <c r="N14" t="n">
-        <v>90.8</v>
+        <v>90.2</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1233,22 +1233,22 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>927</v>
+        <v>961</v>
       </c>
       <c r="K15" t="n">
-        <v>4.019</v>
+        <v>4.065</v>
       </c>
       <c r="L15" t="n">
-        <v>43.1</v>
+        <v>54.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.86</v>
+        <v>3.904</v>
       </c>
       <c r="N15" t="n">
-        <v>7.8</v>
+        <v>11.8</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1288,10 +1288,10 @@
         <v>4.4</v>
       </c>
       <c r="J16" t="n">
-        <v>724</v>
+        <v>754</v>
       </c>
       <c r="K16" t="n">
-        <v>3.974</v>
+        <v>3.975</v>
       </c>
       <c r="L16" t="n">
         <v>29.4</v>
@@ -1300,7 +1300,7 @@
         <v>3.903</v>
       </c>
       <c r="N16" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1337,22 +1337,22 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J17" t="n">
-        <v>1779</v>
+        <v>1793</v>
       </c>
       <c r="K17" t="n">
-        <v>3.821</v>
+        <v>3.856</v>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>3.933</v>
+        <v>3.968</v>
       </c>
       <c r="N17" t="n">
-        <v>14.4</v>
+        <v>17</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1392,7 +1392,7 @@
         <v>4.4</v>
       </c>
       <c r="J18" t="n">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="K18" t="n">
         <v>3.957</v>
@@ -1404,7 +1404,7 @@
         <v>4.072</v>
       </c>
       <c r="N18" t="n">
-        <v>28.1</v>
+        <v>30.7</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1444,19 +1444,19 @@
         <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1031</v>
+        <v>1043</v>
       </c>
       <c r="K19" t="n">
         <v>4.052</v>
       </c>
       <c r="L19" t="n">
-        <v>51.6</v>
+        <v>51</v>
       </c>
       <c r="M19" t="n">
-        <v>4.17</v>
+        <v>4.171</v>
       </c>
       <c r="N19" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1496,19 +1496,19 @@
         <v>4.7</v>
       </c>
       <c r="J20" t="n">
-        <v>633</v>
+        <v>685</v>
       </c>
       <c r="K20" t="n">
-        <v>4.114</v>
+        <v>4.115</v>
       </c>
       <c r="L20" t="n">
-        <v>62.7</v>
+        <v>66</v>
       </c>
       <c r="M20" t="n">
-        <v>4.007</v>
+        <v>4.009</v>
       </c>
       <c r="N20" t="n">
-        <v>19</v>
+        <v>20.9</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1548,19 +1548,19 @@
         <v>4.4</v>
       </c>
       <c r="J21" t="n">
-        <v>672</v>
+        <v>687</v>
       </c>
       <c r="K21" t="n">
-        <v>4.175</v>
+        <v>4.176</v>
       </c>
       <c r="L21" t="n">
-        <v>75.8</v>
+        <v>76.5</v>
       </c>
       <c r="M21" t="n">
-        <v>4.576</v>
+        <v>4.577</v>
       </c>
       <c r="N21" t="n">
-        <v>88.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1600,19 +1600,19 @@
         <v>4.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3966</v>
+        <v>4559</v>
       </c>
       <c r="K22" t="n">
-        <v>4.445</v>
+        <v>4.446</v>
       </c>
       <c r="L22" t="n">
-        <v>98.7</v>
+        <v>99.3</v>
       </c>
       <c r="M22" t="n">
-        <v>4.574</v>
+        <v>4.576</v>
       </c>
       <c r="N22" t="n">
-        <v>88.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1649,27 +1649,27 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
-        <v>442</v>
+        <v>973</v>
       </c>
       <c r="K23" t="n">
-        <v>4.197</v>
+        <v>3.767</v>
       </c>
       <c r="L23" t="n">
-        <v>77.8</v>
+        <v>6.5</v>
       </c>
       <c r="M23" t="n">
-        <v>4.319</v>
+        <v>3.877</v>
       </c>
       <c r="N23" t="n">
-        <v>66</v>
+        <v>8.5</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mido Omakase - West Village</t>
+          <t>Arthur and Sons NY Italian</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1704,16 +1704,16 @@
         <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K24" t="n">
-        <v>3.835</v>
+        <v>3.834</v>
       </c>
       <c r="L24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.947</v>
+        <v>3.946</v>
       </c>
       <c r="N24" t="n">
         <v>15</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1756,13 +1756,13 @@
         <v>4.6</v>
       </c>
       <c r="J25" t="n">
-        <v>2617</v>
+        <v>2667</v>
       </c>
       <c r="K25" t="n">
         <v>4.431</v>
       </c>
       <c r="L25" t="n">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="M25" t="n">
         <v>4.856</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1808,13 +1808,13 @@
         <v>4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="K26" t="n">
         <v>4.023</v>
       </c>
       <c r="L26" t="n">
-        <v>44.4</v>
+        <v>41.8</v>
       </c>
       <c r="M26" t="n">
         <v>3.919</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Manhattan (West Village / Greenwich Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1860,7 +1860,7 @@
         <v>4.7</v>
       </c>
       <c r="J27" t="n">
-        <v>11220</v>
+        <v>11715</v>
       </c>
       <c r="K27" t="n">
         <v>4.498</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (East Village)</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1912,7 +1912,7 @@
         <v>4.5</v>
       </c>
       <c r="J28" t="n">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="K28" t="n">
         <v>4.304</v>
@@ -1924,7 +1924,7 @@
         <v>4.717</v>
       </c>
       <c r="N28" t="n">
-        <v>93.5</v>
+        <v>92.8</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (East Village)</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1964,19 +1964,19 @@
         <v>4.6</v>
       </c>
       <c r="J29" t="n">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="K29" t="n">
         <v>4.266</v>
       </c>
       <c r="L29" t="n">
-        <v>84.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>4.39</v>
       </c>
       <c r="N29" t="n">
-        <v>73.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (East Village)</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2013,27 +2013,27 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J30" t="n">
-        <v>876</v>
+        <v>1298</v>
       </c>
       <c r="K30" t="n">
-        <v>4.075</v>
+        <v>4.01</v>
       </c>
       <c r="L30" t="n">
-        <v>57.5</v>
+        <v>37.3</v>
       </c>
       <c r="M30" t="n">
-        <v>4.194</v>
+        <v>4.127</v>
       </c>
       <c r="N30" t="n">
-        <v>48.4</v>
+        <v>39.9</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Zutto Japanese Ramen Sushi Bar</t>
+          <t>Supper</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (East Village)</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2065,27 +2065,27 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J31" t="n">
-        <v>887</v>
+        <v>737</v>
       </c>
       <c r="K31" t="n">
-        <v>3.757</v>
+        <v>3.618</v>
       </c>
       <c r="L31" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="M31" t="n">
-        <v>3.866</v>
+        <v>3.724</v>
       </c>
       <c r="N31" t="n">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>KYU NYC</t>
+          <t>Cacio e Pepe</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (East Village)</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2120,19 +2120,19 @@
         <v>4.4</v>
       </c>
       <c r="J32" t="n">
-        <v>1353</v>
+        <v>1364</v>
       </c>
       <c r="K32" t="n">
         <v>3.981</v>
       </c>
       <c r="L32" t="n">
-        <v>31.4</v>
+        <v>30.7</v>
       </c>
       <c r="M32" t="n">
-        <v>4.097</v>
+        <v>4.098</v>
       </c>
       <c r="N32" t="n">
-        <v>33.3</v>
+        <v>35.3</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2172,7 +2172,7 @@
         <v>4.4</v>
       </c>
       <c r="J33" t="n">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="K33" t="n">
         <v>4.215</v>
@@ -2184,7 +2184,7 @@
         <v>4.338</v>
       </c>
       <c r="N33" t="n">
-        <v>68</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2224,19 +2224,19 @@
         <v>4.3</v>
       </c>
       <c r="J34" t="n">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="K34" t="n">
-        <v>3.666</v>
+        <v>3.667</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.773</v>
+        <v>3.774</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (Chinatown-Two Bridges)</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2276,19 +2276,19 @@
         <v>4.4</v>
       </c>
       <c r="J35" t="n">
-        <v>4713</v>
+        <v>4820</v>
       </c>
       <c r="K35" t="n">
-        <v>4.018</v>
+        <v>4.019</v>
       </c>
       <c r="L35" t="n">
-        <v>42.5</v>
+        <v>39.9</v>
       </c>
       <c r="M35" t="n">
         <v>4.77</v>
       </c>
       <c r="N35" t="n">
-        <v>96.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2328,7 +2328,7 @@
         <v>4.4</v>
       </c>
       <c r="J36" t="n">
-        <v>910</v>
+        <v>932</v>
       </c>
       <c r="K36" t="n">
         <v>3.953</v>
@@ -2337,10 +2337,10 @@
         <v>24.2</v>
       </c>
       <c r="M36" t="n">
-        <v>4.068</v>
+        <v>4.069</v>
       </c>
       <c r="N36" t="n">
-        <v>26.1</v>
+        <v>29.4</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2377,22 +2377,22 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J37" t="n">
-        <v>1248</v>
+        <v>1290</v>
       </c>
       <c r="K37" t="n">
-        <v>3.729</v>
+        <v>3.774</v>
       </c>
       <c r="L37" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.838</v>
+        <v>3.885</v>
       </c>
       <c r="N37" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2432,24 +2432,24 @@
         <v>4</v>
       </c>
       <c r="J38" t="n">
-        <v>235</v>
+        <v>569</v>
       </c>
       <c r="K38" t="n">
-        <v>3.874</v>
+        <v>3.931</v>
       </c>
       <c r="L38" t="n">
-        <v>11.8</v>
+        <v>20.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.988</v>
+        <v>4.046</v>
       </c>
       <c r="N38" t="n">
-        <v>17.6</v>
+        <v>26.8</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>TOKIODELIC</t>
+          <t>Lodi</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (Upper East Side-Yorkville)</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2484,19 +2484,19 @@
         <v>4.7</v>
       </c>
       <c r="J39" t="n">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="K39" t="n">
-        <v>4.003</v>
+        <v>4.004</v>
       </c>
       <c r="L39" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4.121</v>
+      </c>
+      <c r="N39" t="n">
         <v>37.9</v>
-      </c>
-      <c r="M39" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="N39" t="n">
-        <v>38.6</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2536,13 +2536,13 @@
         <v>4.4</v>
       </c>
       <c r="J40" t="n">
-        <v>3346</v>
+        <v>3389</v>
       </c>
       <c r="K40" t="n">
         <v>4.046</v>
       </c>
       <c r="L40" t="n">
-        <v>48.4</v>
+        <v>47.1</v>
       </c>
       <c r="M40" t="n">
         <v>4.164</v>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2585,27 +2585,27 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J41" t="n">
-        <v>1428</v>
+        <v>1164</v>
       </c>
       <c r="K41" t="n">
-        <v>4.135</v>
+        <v>4.026</v>
       </c>
       <c r="L41" t="n">
-        <v>66.7</v>
+        <v>42.5</v>
       </c>
       <c r="M41" t="n">
-        <v>4.532</v>
+        <v>4.412</v>
       </c>
       <c r="N41" t="n">
-        <v>85.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Momoya SoHo</t>
+          <t>Parm Mulberry Street</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Brooklyn (Carroll Gardens-Cobble Hill-Gowanus-Red Hook)</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2640,19 +2640,19 @@
         <v>4.6</v>
       </c>
       <c r="J42" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K42" t="n">
-        <v>4.125</v>
+        <v>4.129</v>
       </c>
       <c r="L42" t="n">
-        <v>64.7</v>
+        <v>68</v>
       </c>
       <c r="M42" t="n">
-        <v>4.246</v>
+        <v>4.249</v>
       </c>
       <c r="N42" t="n">
-        <v>54.2</v>
+        <v>54.9</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Manhattan (Nolita / SoHo / NoHo / Lower East Side / East Village)</t>
+          <t>Manhattan (East Village)</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2689,27 +2689,27 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="K43" t="n">
-        <v>4.256</v>
+        <v>4.391</v>
       </c>
       <c r="L43" t="n">
-        <v>83.7</v>
+        <v>96.7</v>
       </c>
       <c r="M43" t="n">
-        <v>4.665</v>
+        <v>4.812</v>
       </c>
       <c r="N43" t="n">
-        <v>90.2</v>
+        <v>96.7</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>O Ramen &amp; Dim Sum M Yuki Sushi</t>
+          <t>OLIO E PIÙ East Village</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Tribeca-Civic Center)</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2744,10 +2744,10 @@
         <v>4.4</v>
       </c>
       <c r="J44" t="n">
-        <v>2336</v>
+        <v>2364</v>
       </c>
       <c r="K44" t="n">
-        <v>3.985</v>
+        <v>3.986</v>
       </c>
       <c r="L44" t="n">
         <v>32.7</v>
@@ -2756,7 +2756,7 @@
         <v>3.882</v>
       </c>
       <c r="N44" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Gramercy)</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2796,19 +2796,19 @@
         <v>4.4</v>
       </c>
       <c r="J45" t="n">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="K45" t="n">
-        <v>3.894</v>
+        <v>3.898</v>
       </c>
       <c r="L45" t="n">
-        <v>13.7</v>
+        <v>15</v>
       </c>
       <c r="M45" t="n">
-        <v>3.793</v>
+        <v>3.797</v>
       </c>
       <c r="N45" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Brooklyn (Crown Heights (North))</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2845,22 +2845,22 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J46" t="n">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="K46" t="n">
-        <v>4.15</v>
+        <v>4.115</v>
       </c>
       <c r="L46" t="n">
-        <v>71.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>4.272</v>
+        <v>4.235</v>
       </c>
       <c r="N46" t="n">
-        <v>58.8</v>
+        <v>52.9</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown) (unverified)</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Midtown South-Flatiron-Union Square)</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2939,22 +2939,22 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J48" t="n">
-        <v>1683</v>
+        <v>1792</v>
       </c>
       <c r="K48" t="n">
-        <v>4.225</v>
+        <v>4.27</v>
       </c>
       <c r="L48" t="n">
-        <v>80.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="M48" t="n">
-        <v>4.085</v>
+        <v>4.129</v>
       </c>
       <c r="N48" t="n">
-        <v>31.4</v>
+        <v>40.5</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Midtown South-Flatiron-Union Square)</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2994,19 +2994,19 @@
         <v>4.7</v>
       </c>
       <c r="J49" t="n">
-        <v>6174</v>
+        <v>6676</v>
       </c>
       <c r="K49" t="n">
         <v>4.175</v>
       </c>
       <c r="L49" t="n">
-        <v>75.2</v>
+        <v>75.8</v>
       </c>
       <c r="M49" t="n">
         <v>4.297</v>
       </c>
       <c r="N49" t="n">
-        <v>64.09999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Chelsea-Hudson Yards)</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3046,19 +3046,19 @@
         <v>4.2</v>
       </c>
       <c r="J50" t="n">
-        <v>508</v>
+        <v>538</v>
       </c>
       <c r="K50" t="n">
-        <v>3.915</v>
+        <v>3.916</v>
       </c>
       <c r="L50" t="n">
         <v>17</v>
       </c>
       <c r="M50" t="n">
-        <v>4.029</v>
+        <v>4.031</v>
       </c>
       <c r="N50" t="n">
-        <v>20.3</v>
+        <v>23.5</v>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3098,16 +3098,16 @@
         <v>4.4</v>
       </c>
       <c r="J51" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K51" t="n">
-        <v>3.895</v>
+        <v>3.896</v>
       </c>
       <c r="L51" t="n">
-        <v>14.4</v>
+        <v>13.7</v>
       </c>
       <c r="M51" t="n">
-        <v>3.794</v>
+        <v>3.795</v>
       </c>
       <c r="N51" t="n">
         <v>4.6</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3150,13 +3150,13 @@
         <v>4.4</v>
       </c>
       <c r="J52" t="n">
-        <v>1813</v>
+        <v>1824</v>
       </c>
       <c r="K52" t="n">
         <v>4.015</v>
       </c>
       <c r="L52" t="n">
-        <v>41.8</v>
+        <v>38.6</v>
       </c>
       <c r="M52" t="n">
         <v>3.911</v>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3202,19 +3202,19 @@
         <v>4.5</v>
       </c>
       <c r="J53" t="n">
-        <v>3037</v>
+        <v>3073</v>
       </c>
       <c r="K53" t="n">
         <v>4.145</v>
       </c>
       <c r="L53" t="n">
-        <v>69.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="M53" t="n">
         <v>3.98</v>
       </c>
       <c r="N53" t="n">
-        <v>17</v>
+        <v>18.3</v>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3251,27 +3251,27 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J54" t="n">
-        <v>1238</v>
+        <v>2957</v>
       </c>
       <c r="K54" t="n">
-        <v>3.993</v>
+        <v>4.04</v>
       </c>
       <c r="L54" t="n">
-        <v>35.3</v>
+        <v>45.8</v>
       </c>
       <c r="M54" t="n">
-        <v>3.89</v>
+        <v>3.935</v>
       </c>
       <c r="N54" t="n">
-        <v>10.5</v>
+        <v>13.7</v>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kaiten Zushi Nomad | AYCE Conveyor Belt Sushi, AYCE Sushi, Japanese Restaurant in NYC</t>
+          <t>Quality Italian</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Gramercy)</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3303,22 +3303,22 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J55" t="n">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="K55" t="n">
-        <v>4.162</v>
+        <v>4.134</v>
       </c>
       <c r="L55" t="n">
-        <v>73.2</v>
+        <v>69.3</v>
       </c>
       <c r="M55" t="n">
-        <v>4.054</v>
+        <v>4.027</v>
       </c>
       <c r="N55" t="n">
-        <v>24.2</v>
+        <v>22.2</v>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Midtown South-Flatiron-Union Square)</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3355,27 +3355,27 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J56" t="n">
-        <v>207</v>
+        <v>304</v>
       </c>
       <c r="K56" t="n">
-        <v>4.184</v>
+        <v>4.091</v>
       </c>
       <c r="L56" t="n">
-        <v>77.09999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="M56" t="n">
-        <v>4.076</v>
+        <v>3.985</v>
       </c>
       <c r="N56" t="n">
-        <v>28.8</v>
+        <v>19</v>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Massara On Park</t>
+          <t>Massara</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Upper West Side-Lincoln Square)</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3410,19 +3410,19 @@
         <v>4.2</v>
       </c>
       <c r="J57" t="n">
-        <v>1474</v>
+        <v>1531</v>
       </c>
       <c r="K57" t="n">
-        <v>3.93</v>
+        <v>3.931</v>
       </c>
       <c r="L57" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="M57" t="n">
         <v>3.829</v>
       </c>
       <c r="N57" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (East Midtown-Turtle Bay)</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3459,19 +3459,19 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J58" t="n">
-        <v>933</v>
+        <v>1320</v>
       </c>
       <c r="K58" t="n">
-        <v>3.905</v>
+        <v>3.873</v>
       </c>
       <c r="L58" t="n">
-        <v>15</v>
+        <v>11.8</v>
       </c>
       <c r="M58" t="n">
-        <v>4.019</v>
+        <v>3.986</v>
       </c>
       <c r="N58" t="n">
         <v>19.6</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Chelsea-Hudson Yards)</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -3514,10 +3514,10 @@
         <v>4.6</v>
       </c>
       <c r="J59" t="n">
-        <v>2233</v>
+        <v>2355</v>
       </c>
       <c r="K59" t="n">
-        <v>4.389</v>
+        <v>4.39</v>
       </c>
       <c r="L59" t="n">
         <v>96.09999999999999</v>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Midtown South-Flatiron-Union Square)</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -3566,24 +3566,24 @@
         <v>4.6</v>
       </c>
       <c r="J60" t="n">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="K60" t="n">
-        <v>4.319</v>
+        <v>4.323</v>
       </c>
       <c r="L60" t="n">
         <v>90.8</v>
       </c>
       <c r="M60" t="n">
-        <v>4.445</v>
+        <v>4.449</v>
       </c>
       <c r="N60" t="n">
-        <v>78.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sushi By Bou - NOMAD NYC @ Hotel32|32</t>
+          <t>Tarallucci e Vino NoMad</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3615,27 +3615,27 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J61" t="n">
-        <v>422</v>
+        <v>322</v>
       </c>
       <c r="K61" t="n">
-        <v>4.232</v>
+        <v>4.187</v>
       </c>
       <c r="L61" t="n">
-        <v>81.7</v>
+        <v>77.8</v>
       </c>
       <c r="M61" t="n">
-        <v>4.123</v>
+        <v>4.079</v>
       </c>
       <c r="N61" t="n">
-        <v>39.2</v>
+        <v>31.4</v>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sushi By Bou - NOMAD NYC @ Hotel32|32</t>
+          <t>Santi</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -3670,19 +3670,19 @@
         <v>4.4</v>
       </c>
       <c r="J62" t="n">
-        <v>2721</v>
+        <v>2742</v>
       </c>
       <c r="K62" t="n">
         <v>4.07</v>
       </c>
       <c r="L62" t="n">
-        <v>55.6</v>
+        <v>56.9</v>
       </c>
       <c r="M62" t="n">
-        <v>4.46</v>
+        <v>4.461</v>
       </c>
       <c r="N62" t="n">
-        <v>81</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Hell's Kitchen)</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -3719,27 +3719,27 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J63" t="n">
-        <v>309</v>
+        <v>2223</v>
       </c>
       <c r="K63" t="n">
-        <v>4.164</v>
+        <v>4.127</v>
       </c>
       <c r="L63" t="n">
-        <v>73.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="M63" t="n">
-        <v>4.564</v>
+        <v>4.523</v>
       </c>
       <c r="N63" t="n">
-        <v>87.59999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Domo omakase</t>
+          <t>Don Antonio</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca / Chelsea / Flatiron / Gramercy / NoMad / Midtown)</t>
+          <t>Manhattan (Financial District-Battery Park City)</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -3774,19 +3774,19 @@
         <v>4.6</v>
       </c>
       <c r="J64" t="n">
-        <v>3349</v>
+        <v>3396</v>
       </c>
       <c r="K64" t="n">
         <v>4.138</v>
       </c>
       <c r="L64" t="n">
-        <v>68.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="M64" t="n">
         <v>4.535</v>
       </c>
       <c r="N64" t="n">
-        <v>86.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Manhattan (Upper East Side / Upper West Side / Harlem)</t>
+          <t>Manhattan (East Harlem (North))</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -3826,19 +3826,19 @@
         <v>4.4</v>
       </c>
       <c r="J65" t="n">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="K65" t="n">
         <v>4.137</v>
       </c>
       <c r="L65" t="n">
-        <v>68</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="M65" t="n">
-        <v>4.029</v>
+        <v>4.03</v>
       </c>
       <c r="N65" t="n">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Manhattan (Upper East Side / Upper West Side / Harlem)</t>
+          <t>Manhattan (Upper East Side-Yorkville)</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -3878,13 +3878,13 @@
         <v>4.2</v>
       </c>
       <c r="J66" t="n">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="K66" t="n">
         <v>3.699</v>
       </c>
       <c r="L66" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="M66" t="n">
         <v>3.603</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Manhattan (Upper East Side / Upper West Side / Harlem)</t>
+          <t>Manhattan (Upper East Side-Carnegie Hill)</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -3930,7 +3930,7 @@
         <v>4.3</v>
       </c>
       <c r="J67" t="n">
-        <v>984</v>
+        <v>1002</v>
       </c>
       <c r="K67" t="n">
         <v>3.948</v>
@@ -3942,7 +3942,7 @@
         <v>4.063</v>
       </c>
       <c r="N67" t="n">
-        <v>25.5</v>
+        <v>28.1</v>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Manhattan (Upper East Side / Upper West Side / Harlem)</t>
+          <t>Manhattan (Upper West Side (Central))</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -3982,19 +3982,19 @@
         <v>4.7</v>
       </c>
       <c r="J68" t="n">
-        <v>489</v>
+        <v>512</v>
       </c>
       <c r="K68" t="n">
-        <v>4.25</v>
+        <v>4.251</v>
       </c>
       <c r="L68" t="n">
-        <v>82.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="M68" t="n">
-        <v>4.374</v>
+        <v>4.375</v>
       </c>
       <c r="N68" t="n">
-        <v>71.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Manhattan (Upper East Side / Upper West Side / Harlem)</t>
+          <t>Manhattan (Upper West Side-Lincoln Square)</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -4034,10 +4034,10 @@
         <v>4.4</v>
       </c>
       <c r="J69" t="n">
-        <v>2358</v>
+        <v>2407</v>
       </c>
       <c r="K69" t="n">
-        <v>3.78</v>
+        <v>3.781</v>
       </c>
       <c r="L69" t="n">
         <v>7.8</v>
@@ -4046,7 +4046,7 @@
         <v>3.891</v>
       </c>
       <c r="N69" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Manhattan (Upper East Side / Upper West Side / Harlem)</t>
+          <t>Manhattan (Upper West Side-Lincoln Square)</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -4086,19 +4086,19 @@
         <v>4.3</v>
       </c>
       <c r="J70" t="n">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="K70" t="n">
         <v>3.932</v>
       </c>
       <c r="L70" t="n">
-        <v>20.3</v>
+        <v>20.9</v>
       </c>
       <c r="M70" t="n">
-        <v>3.83</v>
+        <v>3.831</v>
       </c>
       <c r="N70" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Manhattan (Upper East Side / Upper West Side / Harlem)</t>
+          <t>Manhattan (Upper West Side (Central))</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -4138,19 +4138,19 @@
         <v>4.5</v>
       </c>
       <c r="J71" t="n">
-        <v>1015</v>
+        <v>1042</v>
       </c>
       <c r="K71" t="n">
         <v>3.689</v>
       </c>
       <c r="L71" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="M71" t="n">
         <v>4.043</v>
       </c>
       <c r="N71" t="n">
-        <v>22.2</v>
+        <v>25.5</v>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Manhattan (Upper East Side / Upper West Side / Harlem)</t>
+          <t>Manhattan (East Harlem (North))</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -4187,22 +4187,22 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J72" t="n">
-        <v>587</v>
+        <v>3675</v>
       </c>
       <c r="K72" t="n">
-        <v>3.864</v>
+        <v>4.077</v>
       </c>
       <c r="L72" t="n">
-        <v>10.5</v>
+        <v>58.8</v>
       </c>
       <c r="M72" t="n">
-        <v>4.235</v>
+        <v>4.468</v>
       </c>
       <c r="N72" t="n">
-        <v>52.3</v>
+        <v>81.7</v>
       </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Manhattan (Upper East Side / Upper West Side / Harlem)</t>
+          <t>Manhattan (Harlem (South))</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -4242,19 +4242,19 @@
         <v>4.7</v>
       </c>
       <c r="J73" t="n">
-        <v>1563</v>
+        <v>1576</v>
       </c>
       <c r="K73" t="n">
         <v>4.105</v>
       </c>
       <c r="L73" t="n">
-        <v>60.8</v>
+        <v>63.4</v>
       </c>
       <c r="M73" t="n">
-        <v>4.498</v>
+        <v>4.499</v>
       </c>
       <c r="N73" t="n">
-        <v>83.7</v>
+        <v>84.3</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Brooklyn (Williamsburg / Greenpoint)</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4294,19 +4294,19 @@
         <v>4.3</v>
       </c>
       <c r="J74" t="n">
-        <v>2277</v>
+        <v>2301</v>
       </c>
       <c r="K74" t="n">
         <v>4.05</v>
       </c>
       <c r="L74" t="n">
-        <v>50.3</v>
+        <v>49.7</v>
       </c>
       <c r="M74" t="n">
         <v>4.071</v>
       </c>
       <c r="N74" t="n">
-        <v>27.5</v>
+        <v>30.1</v>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Brooklyn (Williamsburg / Greenpoint)</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4346,10 +4346,10 @@
         <v>4.3</v>
       </c>
       <c r="J75" t="n">
-        <v>1850</v>
+        <v>1881</v>
       </c>
       <c r="K75" t="n">
-        <v>4.057</v>
+        <v>4.058</v>
       </c>
       <c r="L75" t="n">
         <v>52.9</v>
@@ -4358,7 +4358,7 @@
         <v>4.124</v>
       </c>
       <c r="N75" t="n">
-        <v>40.5</v>
+        <v>38.6</v>
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Brooklyn (Williamsburg / Greenpoint)</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -4398,19 +4398,19 @@
         <v>4.5</v>
       </c>
       <c r="J76" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="K76" t="n">
-        <v>3.958</v>
+        <v>3.968</v>
       </c>
       <c r="L76" t="n">
-        <v>26.1</v>
+        <v>26.8</v>
       </c>
       <c r="M76" t="n">
-        <v>3.958</v>
+        <v>3.968</v>
       </c>
       <c r="N76" t="n">
-        <v>15.7</v>
+        <v>16.3</v>
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Brooklyn (Williamsburg / Greenpoint)</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -4450,19 +4450,19 @@
         <v>4.5</v>
       </c>
       <c r="J77" t="n">
-        <v>1322</v>
+        <v>1345</v>
       </c>
       <c r="K77" t="n">
         <v>4.051</v>
       </c>
       <c r="L77" t="n">
-        <v>51</v>
+        <v>50.3</v>
       </c>
       <c r="M77" t="n">
-        <v>4.169</v>
+        <v>4.17</v>
       </c>
       <c r="N77" t="n">
-        <v>45.1</v>
+        <v>45.8</v>
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Brooklyn (Williamsburg / Greenpoint)</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -4502,7 +4502,7 @@
         <v>4.5</v>
       </c>
       <c r="J78" t="n">
-        <v>1598</v>
+        <v>1617</v>
       </c>
       <c r="K78" t="n">
         <v>4.223</v>
@@ -4514,7 +4514,7 @@
         <v>4.346</v>
       </c>
       <c r="N78" t="n">
-        <v>68.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Brooklyn (Williamsburg / Greenpoint)</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -4551,27 +4551,27 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
-        <v>440</v>
+        <v>518</v>
       </c>
       <c r="K79" t="n">
-        <v>3.987</v>
+        <v>3.858</v>
       </c>
       <c r="L79" t="n">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="M79" t="n">
-        <v>4.104</v>
+        <v>3.971</v>
       </c>
       <c r="N79" t="n">
-        <v>34.6</v>
+        <v>17.6</v>
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sapporo Ichiban</t>
+          <t>Fabbrica | The Factory</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Brooklyn (Williamsburg / Greenpoint)</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -4606,10 +4606,10 @@
         <v>4.4</v>
       </c>
       <c r="J80" t="n">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="K80" t="n">
-        <v>3.909</v>
+        <v>3.91</v>
       </c>
       <c r="L80" t="n">
         <v>16.3</v>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Brooklyn (Williamsburg / Greenpoint)</t>
+          <t>Brooklyn (Downtown Brooklyn-DUMBO-Boerum Hill)</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -4655,27 +4655,27 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J81" t="n">
-        <v>440</v>
+        <v>1221</v>
       </c>
       <c r="K81" t="n">
-        <v>4.023</v>
+        <v>4.14</v>
       </c>
       <c r="L81" t="n">
-        <v>45.1</v>
+        <v>72.5</v>
       </c>
       <c r="M81" t="n">
-        <v>4.409</v>
+        <v>4.537</v>
       </c>
       <c r="N81" t="n">
-        <v>75.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sapporo Ichiban</t>
+          <t>Sottocasa</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Brooklyn (Carroll Gardens / Cobble Hill / Boerum Hill)</t>
+          <t>Brooklyn (Carroll Gardens-Cobble Hill-Gowanus-Red Hook)</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -4710,13 +4710,13 @@
         <v>4.5</v>
       </c>
       <c r="J82" t="n">
-        <v>1465</v>
+        <v>1483</v>
       </c>
       <c r="K82" t="n">
-        <v>4.107</v>
+        <v>4.108</v>
       </c>
       <c r="L82" t="n">
-        <v>62.1</v>
+        <v>64.7</v>
       </c>
       <c r="M82" t="n">
         <v>4.288</v>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Brooklyn (Carroll Gardens / Cobble Hill / Boerum Hill)</t>
+          <t>Brooklyn (Carroll Gardens-Cobble Hill-Gowanus-Red Hook)</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -4762,19 +4762,19 @@
         <v>4.5</v>
       </c>
       <c r="J83" t="n">
-        <v>683</v>
+        <v>707</v>
       </c>
       <c r="K83" t="n">
-        <v>4.026</v>
+        <v>4.027</v>
       </c>
       <c r="L83" t="n">
-        <v>45.8</v>
+        <v>43.1</v>
       </c>
       <c r="M83" t="n">
-        <v>4.779</v>
+        <v>4.78</v>
       </c>
       <c r="N83" t="n">
-        <v>96.7</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Brooklyn (Carroll Gardens / Cobble Hill / Boerum Hill)</t>
+          <t>Brooklyn (Carroll Gardens-Cobble Hill-Gowanus-Red Hook)</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -4814,19 +4814,19 @@
         <v>4.7</v>
       </c>
       <c r="J84" t="n">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="K84" t="n">
-        <v>4.056</v>
+        <v>4.057</v>
       </c>
       <c r="L84" t="n">
-        <v>52.3</v>
+        <v>51.6</v>
       </c>
       <c r="M84" t="n">
         <v>4.175</v>
       </c>
       <c r="N84" t="n">
-        <v>46.4</v>
+        <v>47.1</v>
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Brooklyn (Carroll Gardens / Cobble Hill / Boerum Hill)</t>
+          <t>Brooklyn (Carroll Gardens-Cobble Hill-Gowanus-Red Hook)</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -4866,19 +4866,19 @@
         <v>4.9</v>
       </c>
       <c r="J85" t="n">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="K85" t="n">
         <v>4.356</v>
       </c>
       <c r="L85" t="n">
-        <v>94.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="M85" t="n">
-        <v>4.483</v>
+        <v>4.484</v>
       </c>
       <c r="N85" t="n">
-        <v>83</v>
+        <v>83.7</v>
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Brooklyn (Carroll Gardens / Cobble Hill / Boerum Hill)</t>
+          <t>Brooklyn (Carroll Gardens-Cobble Hill-Gowanus-Red Hook)</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -4918,7 +4918,7 @@
         <v>4.2</v>
       </c>
       <c r="J86" t="n">
-        <v>3059</v>
+        <v>3080</v>
       </c>
       <c r="K86" t="n">
         <v>4.306</v>
@@ -4930,7 +4930,7 @@
         <v>4.432</v>
       </c>
       <c r="N86" t="n">
-        <v>77.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Brooklyn (Carroll Gardens / Cobble Hill / Boerum Hill)</t>
+          <t>Brooklyn (Carroll Gardens-Cobble Hill-Gowanus-Red Hook)</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -4970,19 +4970,19 @@
         <v>4.6</v>
       </c>
       <c r="J87" t="n">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="K87" t="n">
         <v>4.013</v>
       </c>
       <c r="L87" t="n">
-        <v>40.5</v>
+        <v>37.9</v>
       </c>
       <c r="M87" t="n">
         <v>4.13</v>
       </c>
       <c r="N87" t="n">
-        <v>41.8</v>
+        <v>41.2</v>
       </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Brooklyn (Carroll Gardens / Cobble Hill / Boerum Hill)</t>
+          <t>Brooklyn (Carroll Gardens-Cobble Hill-Gowanus-Red Hook)</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -5022,19 +5022,19 @@
         <v>4.6</v>
       </c>
       <c r="J88" t="n">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="K88" t="n">
-        <v>4.015</v>
+        <v>4.016</v>
       </c>
       <c r="L88" t="n">
-        <v>41.2</v>
+        <v>39.2</v>
       </c>
       <c r="M88" t="n">
-        <v>4.766</v>
+        <v>4.767</v>
       </c>
       <c r="N88" t="n">
-        <v>95.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Brooklyn (Carroll Gardens / Cobble Hill / Boerum Hill)</t>
+          <t>Brooklyn (Brooklyn Heights)</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -5074,24 +5074,24 @@
         <v>4.4</v>
       </c>
       <c r="J89" t="n">
-        <v>285</v>
+        <v>738</v>
       </c>
       <c r="K89" t="n">
-        <v>3.994</v>
+        <v>4.021</v>
       </c>
       <c r="L89" t="n">
-        <v>36.6</v>
+        <v>41.2</v>
       </c>
       <c r="M89" t="n">
-        <v>4.11</v>
+        <v>4.138</v>
       </c>
       <c r="N89" t="n">
-        <v>36.6</v>
+        <v>41.8</v>
       </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>SOBOKU</t>
+          <t>Noodle Pudding</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Brooklyn (Carroll Gardens / Cobble Hill / Boerum Hill)</t>
+          <t>Brooklyn (Brooklyn Heights)</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -5123,27 +5123,27 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="J90" t="n">
-        <v>90</v>
+        <v>602</v>
       </c>
       <c r="K90" t="n">
-        <v>4.131</v>
+        <v>3.927</v>
       </c>
       <c r="L90" t="n">
-        <v>65.40000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="M90" t="n">
-        <v>4.251</v>
+        <v>4.041</v>
       </c>
       <c r="N90" t="n">
-        <v>54.9</v>
+        <v>24.8</v>
       </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Koju</t>
+          <t>River Deli</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Brooklyn (Park Slope / Gowanus / Prospect Heights)</t>
+          <t>Brooklyn (Park Slope)</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -5175,27 +5175,27 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J91" t="n">
-        <v>422</v>
+        <v>1086</v>
       </c>
       <c r="K91" t="n">
-        <v>4.171</v>
+        <v>4.057</v>
       </c>
       <c r="L91" t="n">
-        <v>74.5</v>
+        <v>52.3</v>
       </c>
       <c r="M91" t="n">
-        <v>4.293</v>
+        <v>4.176</v>
       </c>
       <c r="N91" t="n">
-        <v>62.7</v>
+        <v>47.7</v>
       </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sushi Lin Park Slope</t>
+          <t>al di là Trattoria</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Brooklyn (Park Slope / Gowanus / Prospect Heights)</t>
+          <t>Brooklyn (Carroll Gardens-Cobble Hill-Gowanus-Red Hook)</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -5230,16 +5230,16 @@
         <v>4.8</v>
       </c>
       <c r="J92" t="n">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="K92" t="n">
-        <v>4.417</v>
+        <v>4.418</v>
       </c>
       <c r="L92" t="n">
-        <v>96.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="M92" t="n">
-        <v>4.841</v>
+        <v>4.842</v>
       </c>
       <c r="N92" t="n">
         <v>97.40000000000001</v>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Brooklyn (Bushwick / Bed-Stuy / Crown Heights)</t>
+          <t>Brooklyn (East Williamsburg)</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -5282,19 +5282,19 @@
         <v>4.4</v>
       </c>
       <c r="J93" t="n">
-        <v>2137</v>
+        <v>2175</v>
       </c>
       <c r="K93" t="n">
         <v>4.066</v>
       </c>
       <c r="L93" t="n">
-        <v>54.2</v>
+        <v>54.9</v>
       </c>
       <c r="M93" t="n">
         <v>4.456</v>
       </c>
       <c r="N93" t="n">
-        <v>79.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Brooklyn (Bushwick / Bed-Stuy / Crown Heights)</t>
+          <t>Brooklyn (Bushwick (West))</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -5331,27 +5331,27 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J94" t="n">
-        <v>41</v>
+        <v>604</v>
       </c>
       <c r="K94" t="n">
-        <v>3.993</v>
+        <v>4.296</v>
       </c>
       <c r="L94" t="n">
-        <v>35.9</v>
+        <v>86.3</v>
       </c>
       <c r="M94" t="n">
-        <v>4.11</v>
+        <v>4.421</v>
       </c>
       <c r="N94" t="n">
-        <v>35.9</v>
+        <v>74.5</v>
       </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>The Faro Sports Bar</t>
+          <t>Faro</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Brooklyn (Bushwick / Bed-Stuy / Crown Heights)</t>
+          <t>Brooklyn (Bedford-Stuyvesant (East))</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -5386,19 +5386,19 @@
         <v>4.5</v>
       </c>
       <c r="J95" t="n">
-        <v>2313</v>
+        <v>2326</v>
       </c>
       <c r="K95" t="n">
         <v>4.072</v>
       </c>
       <c r="L95" t="n">
-        <v>56.9</v>
+        <v>58.2</v>
       </c>
       <c r="M95" t="n">
         <v>4.463</v>
       </c>
       <c r="N95" t="n">
-        <v>81.7</v>
+        <v>81</v>
       </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Coney Island-Sea Gate)</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -5438,19 +5438,19 @@
         <v>4.4</v>
       </c>
       <c r="J96" t="n">
-        <v>1632</v>
+        <v>1656</v>
       </c>
       <c r="K96" t="n">
-        <v>3.972</v>
+        <v>3.973</v>
       </c>
       <c r="L96" t="n">
         <v>28.8</v>
       </c>
       <c r="M96" t="n">
-        <v>3.869</v>
+        <v>3.87</v>
       </c>
       <c r="N96" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Gravesend (West))</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -5490,7 +5490,7 @@
         <v>4.6</v>
       </c>
       <c r="J97" t="n">
-        <v>11345</v>
+        <v>11452</v>
       </c>
       <c r="K97" t="n">
         <v>4.334</v>
@@ -5502,7 +5502,7 @@
         <v>4.749</v>
       </c>
       <c r="N97" t="n">
-        <v>94.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Bensonhurst)</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -5542,10 +5542,10 @@
         <v>4.5</v>
       </c>
       <c r="J98" t="n">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="K98" t="n">
-        <v>3.924</v>
+        <v>3.925</v>
       </c>
       <c r="L98" t="n">
         <v>17.6</v>
@@ -5554,7 +5554,7 @@
         <v>4.039</v>
       </c>
       <c r="N98" t="n">
-        <v>21.6</v>
+        <v>24.2</v>
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Bensonhurst)</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -5594,19 +5594,19 @@
         <v>4.5</v>
       </c>
       <c r="J99" t="n">
-        <v>774</v>
+        <v>787</v>
       </c>
       <c r="K99" t="n">
         <v>4.292</v>
       </c>
       <c r="L99" t="n">
-        <v>86.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M99" t="n">
         <v>4.417</v>
       </c>
       <c r="N99" t="n">
-        <v>75.8</v>
+        <v>73.2</v>
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Bensonhurst)</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -5646,19 +5646,19 @@
         <v>4.6</v>
       </c>
       <c r="J100" t="n">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="K100" t="n">
         <v>4.089</v>
       </c>
       <c r="L100" t="n">
-        <v>59.5</v>
+        <v>61.4</v>
       </c>
       <c r="M100" t="n">
-        <v>4.208</v>
+        <v>4.209</v>
       </c>
       <c r="N100" t="n">
-        <v>50.3</v>
+        <v>51</v>
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Sheepshead Bay-Manhattan Beach-Gerritsen Beach)</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -5698,19 +5698,19 @@
         <v>4.3</v>
       </c>
       <c r="J101" t="n">
-        <v>2884</v>
+        <v>2924</v>
       </c>
       <c r="K101" t="n">
         <v>3.759</v>
       </c>
       <c r="L101" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="M101" t="n">
         <v>4.12</v>
       </c>
       <c r="N101" t="n">
-        <v>37.9</v>
+        <v>36.6</v>
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Madison)</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -5750,13 +5750,13 @@
         <v>4.7</v>
       </c>
       <c r="J102" t="n">
-        <v>1736</v>
+        <v>1749</v>
       </c>
       <c r="K102" t="n">
         <v>4.135</v>
       </c>
       <c r="L102" t="n">
-        <v>67.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M102" t="n">
         <v>4.256</v>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Midwood)</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -5802,19 +5802,19 @@
         <v>4.2</v>
       </c>
       <c r="J103" t="n">
-        <v>4643</v>
+        <v>4683</v>
       </c>
       <c r="K103" t="n">
         <v>4.069</v>
       </c>
       <c r="L103" t="n">
-        <v>54.9</v>
+        <v>56.2</v>
       </c>
       <c r="M103" t="n">
-        <v>4.459</v>
+        <v>4.46</v>
       </c>
       <c r="N103" t="n">
-        <v>80.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Bay Ridge)</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -5854,13 +5854,13 @@
         <v>4.5</v>
       </c>
       <c r="J104" t="n">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="K104" t="n">
-        <v>3.684</v>
+        <v>3.685</v>
       </c>
       <c r="L104" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M104" t="n">
         <v>3.589</v>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Bay Ridge)</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -5906,19 +5906,19 @@
         <v>4.6</v>
       </c>
       <c r="J105" t="n">
-        <v>2380</v>
+        <v>2401</v>
       </c>
       <c r="K105" t="n">
         <v>4.104</v>
       </c>
       <c r="L105" t="n">
-        <v>60.1</v>
+        <v>62.7</v>
       </c>
       <c r="M105" t="n">
         <v>4.224</v>
       </c>
       <c r="N105" t="n">
-        <v>51</v>
+        <v>51.6</v>
       </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Bay Ridge)</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -5958,16 +5958,16 @@
         <v>4.5</v>
       </c>
       <c r="J106" t="n">
-        <v>1336</v>
+        <v>1362</v>
       </c>
       <c r="K106" t="n">
         <v>4.046</v>
       </c>
       <c r="L106" t="n">
-        <v>49</v>
+        <v>47.7</v>
       </c>
       <c r="M106" t="n">
-        <v>4.164</v>
+        <v>4.165</v>
       </c>
       <c r="N106" t="n">
         <v>44.4</v>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Bay Ridge)</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -6007,27 +6007,27 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J107" t="n">
-        <v>643</v>
+        <v>205</v>
       </c>
       <c r="K107" t="n">
-        <v>3.929</v>
+        <v>4.044</v>
       </c>
       <c r="L107" t="n">
-        <v>18.3</v>
+        <v>46.4</v>
       </c>
       <c r="M107" t="n">
-        <v>4.306</v>
+        <v>4.432</v>
       </c>
       <c r="N107" t="n">
-        <v>64.7</v>
+        <v>75.8</v>
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Bayridge Sushi</t>
+          <t>Lombardo’s of Bay Ridge</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Bay Ridge)</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -6062,19 +6062,19 @@
         <v>4.5</v>
       </c>
       <c r="J108" t="n">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="K108" t="n">
         <v>3.675</v>
       </c>
       <c r="L108" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="M108" t="n">
         <v>3.782</v>
       </c>
       <c r="N108" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Brooklyn (Coney Island / Gravesend / Bensonhurst / Bay Ridge / Mapleton)</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -6114,7 +6114,7 @@
         <v>4.4</v>
       </c>
       <c r="J109" t="n">
-        <v>1049</v>
+        <v>1064</v>
       </c>
       <c r="K109" t="n">
         <v>3.985</v>
@@ -6123,10 +6123,10 @@
         <v>32</v>
       </c>
       <c r="M109" t="n">
-        <v>4.101</v>
+        <v>4.102</v>
       </c>
       <c r="N109" t="n">
-        <v>34</v>
+        <v>35.9</v>
       </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Brooklyn (Fort Greene / DUMBO)</t>
+          <t>Brooklyn (Fort Greene)</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -6166,19 +6166,19 @@
         <v>4.7</v>
       </c>
       <c r="J110" t="n">
-        <v>1217</v>
+        <v>1240</v>
       </c>
       <c r="K110" t="n">
         <v>4.124</v>
       </c>
       <c r="L110" t="n">
-        <v>63.4</v>
+        <v>66.7</v>
       </c>
       <c r="M110" t="n">
         <v>4.244</v>
       </c>
       <c r="N110" t="n">
-        <v>53.6</v>
+        <v>54.2</v>
       </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Brooklyn (Fort Greene / DUMBO)</t>
+          <t>Brooklyn (Clinton Hill)</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -6218,19 +6218,19 @@
         <v>4.5</v>
       </c>
       <c r="J111" t="n">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="K111" t="n">
         <v>4.008</v>
       </c>
       <c r="L111" t="n">
-        <v>39.9</v>
+        <v>36.6</v>
       </c>
       <c r="M111" t="n">
         <v>4.125</v>
       </c>
       <c r="N111" t="n">
-        <v>41.2</v>
+        <v>39.2</v>
       </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Brooklyn (Fort Greene / DUMBO)</t>
+          <t>Brooklyn (Downtown Brooklyn-DUMBO-Boerum Hill)</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -6270,7 +6270,7 @@
         <v>4.1</v>
       </c>
       <c r="J112" t="n">
-        <v>3165</v>
+        <v>3239</v>
       </c>
       <c r="K112" t="n">
         <v>3.908</v>
@@ -6282,7 +6282,7 @@
         <v>3.807</v>
       </c>
       <c r="N112" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Brooklyn (Fort Greene / DUMBO)</t>
+          <t>Brooklyn (Downtown Brooklyn-DUMBO-Boerum Hill)</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -6322,7 +6322,7 @@
         <v>4.6</v>
       </c>
       <c r="J113" t="n">
-        <v>6811</v>
+        <v>6908</v>
       </c>
       <c r="K113" t="n">
         <v>4.302</v>
@@ -6334,7 +6334,7 @@
         <v>4.715</v>
       </c>
       <c r="N113" t="n">
-        <v>92.8</v>
+        <v>92.2</v>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Brooklyn (Fort Greene / DUMBO)</t>
+          <t>Brooklyn (Downtown Brooklyn-DUMBO-Boerum Hill)</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -6374,19 +6374,19 @@
         <v>4.2</v>
       </c>
       <c r="J114" t="n">
-        <v>9611</v>
+        <v>9671</v>
       </c>
       <c r="K114" t="n">
         <v>3.725</v>
       </c>
       <c r="L114" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="M114" t="n">
         <v>4.082</v>
       </c>
       <c r="N114" t="n">
-        <v>30.7</v>
+        <v>33.3</v>
       </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Corona)</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -6426,19 +6426,19 @@
         <v>4.6</v>
       </c>
       <c r="J115" t="n">
-        <v>3310</v>
+        <v>3332</v>
       </c>
       <c r="K115" t="n">
         <v>4.085</v>
       </c>
       <c r="L115" t="n">
-        <v>58.2</v>
+        <v>60.1</v>
       </c>
       <c r="M115" t="n">
         <v>4.204</v>
       </c>
       <c r="N115" t="n">
-        <v>49</v>
+        <v>49.7</v>
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Manhattan (Upper East Side-Yorkville)</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -6478,13 +6478,13 @@
         <v>4.7</v>
       </c>
       <c r="J116" t="n">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="K116" t="n">
         <v>4.157</v>
       </c>
       <c r="L116" t="n">
-        <v>71.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="M116" t="n">
         <v>4.278</v>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (South Ozone Park)</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -6530,19 +6530,19 @@
         <v>4.5</v>
       </c>
       <c r="J117" t="n">
-        <v>1549</v>
+        <v>1571</v>
       </c>
       <c r="K117" t="n">
-        <v>4.085</v>
+        <v>4.086</v>
       </c>
       <c r="L117" t="n">
-        <v>58.8</v>
+        <v>60.8</v>
       </c>
       <c r="M117" t="n">
         <v>4.205</v>
       </c>
       <c r="N117" t="n">
-        <v>49.7</v>
+        <v>50.3</v>
       </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Long Island City-Hunters Point)</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -6582,16 +6582,16 @@
         <v>4.6</v>
       </c>
       <c r="J118" t="n">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="K118" t="n">
-        <v>4.002</v>
+        <v>4.003</v>
       </c>
       <c r="L118" t="n">
-        <v>37.3</v>
+        <v>34</v>
       </c>
       <c r="M118" t="n">
-        <v>4.119</v>
+        <v>4.12</v>
       </c>
       <c r="N118" t="n">
         <v>37.3</v>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Long Island City-Hunters Point)</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -6634,7 +6634,7 @@
         <v>4.5</v>
       </c>
       <c r="J119" t="n">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="K119" t="n">
         <v>3.986</v>
@@ -6643,10 +6643,10 @@
         <v>33.3</v>
       </c>
       <c r="M119" t="n">
-        <v>4.368</v>
+        <v>4.369</v>
       </c>
       <c r="N119" t="n">
-        <v>70.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Old Astoria-Hallets Point)</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -6683,27 +6683,27 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J120" t="n">
-        <v>1146</v>
+        <v>655</v>
       </c>
       <c r="K120" t="n">
-        <v>4.125</v>
+        <v>4.078</v>
       </c>
       <c r="L120" t="n">
-        <v>64.09999999999999</v>
+        <v>59.5</v>
       </c>
       <c r="M120" t="n">
-        <v>4.52</v>
+        <v>4.469</v>
       </c>
       <c r="N120" t="n">
-        <v>84.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Watawa Sushi</t>
+          <t>Vesta Trattoria &amp; Wine Bar</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Astoria (Central))</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -6738,7 +6738,7 @@
         <v>4.6</v>
       </c>
       <c r="J121" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="K121" t="n">
         <v>4.328</v>
@@ -6750,7 +6750,7 @@
         <v>4.743</v>
       </c>
       <c r="N121" t="n">
-        <v>94.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Astoria (Central))</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -6787,27 +6787,27 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J122" t="n">
-        <v>3068</v>
+        <v>809</v>
       </c>
       <c r="K122" t="n">
-        <v>4.448</v>
+        <v>4.382</v>
       </c>
       <c r="L122" t="n">
-        <v>99.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="M122" t="n">
-        <v>4.578</v>
+        <v>4.509</v>
       </c>
       <c r="N122" t="n">
-        <v>89.5</v>
+        <v>85</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>What the fish</t>
+          <t>VITE vinosteria</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Astoria (Central))</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -6842,19 +6842,19 @@
         <v>4.4</v>
       </c>
       <c r="J123" t="n">
-        <v>731</v>
+        <v>766</v>
       </c>
       <c r="K123" t="n">
-        <v>4.279</v>
+        <v>4.28</v>
       </c>
       <c r="L123" t="n">
-        <v>86.3</v>
+        <v>85</v>
       </c>
       <c r="M123" t="n">
-        <v>4.404</v>
+        <v>4.405</v>
       </c>
       <c r="N123" t="n">
-        <v>73.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Astoria (North)-Ditmars-Steinway)</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -6894,13 +6894,13 @@
         <v>4.3</v>
       </c>
       <c r="J124" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K124" t="n">
         <v>4.159</v>
       </c>
       <c r="L124" t="n">
-        <v>72.5</v>
+        <v>75.2</v>
       </c>
       <c r="M124" t="n">
         <v>4.28</v>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Astoria (Central))</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -6943,22 +6943,22 @@
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J125" t="n">
-        <v>597</v>
+        <v>607</v>
       </c>
       <c r="K125" t="n">
-        <v>4.023</v>
+        <v>4.069</v>
       </c>
       <c r="L125" t="n">
-        <v>43.8</v>
+        <v>55.6</v>
       </c>
       <c r="M125" t="n">
-        <v>4.409</v>
+        <v>4.459</v>
       </c>
       <c r="N125" t="n">
-        <v>74.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Astoria (Central))</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -6998,19 +6998,19 @@
         <v>4.9</v>
       </c>
       <c r="J126" t="n">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="K126" t="n">
-        <v>4.036</v>
+        <v>4.047</v>
       </c>
       <c r="L126" t="n">
-        <v>47.7</v>
+        <v>48.4</v>
       </c>
       <c r="M126" t="n">
-        <v>3.931</v>
+        <v>3.942</v>
       </c>
       <c r="N126" t="n">
-        <v>13.7</v>
+        <v>14.4</v>
       </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Forest Hills)</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -7056,13 +7056,13 @@
         <v>4.256</v>
       </c>
       <c r="L127" t="n">
-        <v>83</v>
+        <v>81.7</v>
       </c>
       <c r="M127" t="n">
         <v>4.38</v>
       </c>
       <c r="N127" t="n">
-        <v>71.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Howard Beach-Lindenwood)</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -7102,19 +7102,19 @@
         <v>4.7</v>
       </c>
       <c r="J128" t="n">
-        <v>1019</v>
+        <v>1032</v>
       </c>
       <c r="K128" t="n">
-        <v>4.107</v>
+        <v>4.108</v>
       </c>
       <c r="L128" t="n">
-        <v>61.4</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M128" t="n">
         <v>4.227</v>
       </c>
       <c r="N128" t="n">
-        <v>51.6</v>
+        <v>52.3</v>
       </c>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Howard Beach-Lindenwood)</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -7154,19 +7154,19 @@
         <v>4.6</v>
       </c>
       <c r="J129" t="n">
-        <v>1773</v>
+        <v>1799</v>
       </c>
       <c r="K129" t="n">
         <v>4.38</v>
       </c>
       <c r="L129" t="n">
-        <v>95.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="M129" t="n">
         <v>4.267</v>
       </c>
       <c r="N129" t="n">
-        <v>58.2</v>
+        <v>58.8</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Howard Beach-Lindenwood)</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -7206,19 +7206,19 @@
         <v>4.4</v>
       </c>
       <c r="J130" t="n">
-        <v>3285</v>
+        <v>3317</v>
       </c>
       <c r="K130" t="n">
         <v>4.048</v>
       </c>
       <c r="L130" t="n">
-        <v>49.7</v>
+        <v>49</v>
       </c>
       <c r="M130" t="n">
         <v>4.436</v>
       </c>
       <c r="N130" t="n">
-        <v>77.8</v>
+        <v>76.5</v>
       </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Howard Beach-Lindenwood)</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -7258,19 +7258,19 @@
         <v>4.4</v>
       </c>
       <c r="J131" t="n">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="K131" t="n">
         <v>3.945</v>
       </c>
       <c r="L131" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="M131" t="n">
         <v>4.06</v>
       </c>
       <c r="N131" t="n">
-        <v>24.8</v>
+        <v>27.5</v>
       </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Bay Terrace-Clearview)</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -7307,27 +7307,27 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J132" t="n">
-        <v>931</v>
+        <v>695</v>
       </c>
       <c r="K132" t="n">
-        <v>3.762</v>
+        <v>4.02</v>
       </c>
       <c r="L132" t="n">
-        <v>7.2</v>
+        <v>40.5</v>
       </c>
       <c r="M132" t="n">
-        <v>4.123</v>
+        <v>4.406</v>
       </c>
       <c r="N132" t="n">
-        <v>39.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>River Japanese Cuisine - Flushing</t>
+          <t>Riviera Ristorante</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Douglaston-Little Neck)</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -7362,7 +7362,7 @@
         <v>4.4</v>
       </c>
       <c r="J133" t="n">
-        <v>1298</v>
+        <v>1317</v>
       </c>
       <c r="K133" t="n">
         <v>3.976</v>
@@ -7374,7 +7374,7 @@
         <v>4.092</v>
       </c>
       <c r="N133" t="n">
-        <v>32.7</v>
+        <v>34.6</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Middle Village)</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -7414,7 +7414,7 @@
         <v>4.4</v>
       </c>
       <c r="J134" t="n">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K134" t="n">
         <v>3.97</v>
@@ -7423,10 +7423,10 @@
         <v>27.5</v>
       </c>
       <c r="M134" t="n">
-        <v>4.712</v>
+        <v>4.713</v>
       </c>
       <c r="N134" t="n">
-        <v>92.2</v>
+        <v>91.5</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Astoria (Central))</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -7466,19 +7466,19 @@
         <v>4.7</v>
       </c>
       <c r="J135" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K135" t="n">
-        <v>4.149</v>
+        <v>4.151</v>
       </c>
       <c r="L135" t="n">
-        <v>70.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M135" t="n">
-        <v>4.547</v>
+        <v>4.549</v>
       </c>
       <c r="N135" t="n">
-        <v>86.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Astoria (Central))</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -7518,19 +7518,19 @@
         <v>4.5</v>
       </c>
       <c r="J136" t="n">
-        <v>893</v>
+        <v>917</v>
       </c>
       <c r="K136" t="n">
-        <v>4.269</v>
+        <v>4.27</v>
       </c>
       <c r="L136" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M136" t="n">
-        <v>4.679</v>
+        <v>4.68</v>
       </c>
       <c r="N136" t="n">
-        <v>91.5</v>
+        <v>90.8</v>
       </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Astoria (North)-Ditmars-Steinway)</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -7570,19 +7570,19 @@
         <v>4.9</v>
       </c>
       <c r="J137" t="n">
-        <v>4111</v>
+        <v>4316</v>
       </c>
       <c r="K137" t="n">
         <v>4.133</v>
       </c>
       <c r="L137" t="n">
-        <v>66</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M137" t="n">
         <v>4.529</v>
       </c>
       <c r="N137" t="n">
-        <v>85</v>
+        <v>86.3</v>
       </c>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Queens (Astoria (North)-Ditmars-Steinway)</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -7622,7 +7622,7 @@
         <v>4.4</v>
       </c>
       <c r="J138" t="n">
-        <v>707</v>
+        <v>727</v>
       </c>
       <c r="K138" t="n">
         <v>3.956</v>
@@ -7631,10 +7631,10 @@
         <v>24.8</v>
       </c>
       <c r="M138" t="n">
-        <v>4.335</v>
+        <v>4.336</v>
       </c>
       <c r="N138" t="n">
-        <v>67.3</v>
+        <v>64.7</v>
       </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Belmont)</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -7671,22 +7671,22 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J139" t="n">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="K139" t="n">
-        <v>3.992</v>
+        <v>4.038</v>
       </c>
       <c r="L139" t="n">
-        <v>34.6</v>
+        <v>45.1</v>
       </c>
       <c r="M139" t="n">
-        <v>4.109</v>
+        <v>4.156</v>
       </c>
       <c r="N139" t="n">
-        <v>35.3</v>
+        <v>43.1</v>
       </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Belmont)</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -7726,13 +7726,13 @@
         <v>4.5</v>
       </c>
       <c r="J140" t="n">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="K140" t="n">
-        <v>4.027</v>
+        <v>4.028</v>
       </c>
       <c r="L140" t="n">
-        <v>46.4</v>
+        <v>43.8</v>
       </c>
       <c r="M140" t="n">
         <v>4.145</v>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Belmont)</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -7778,7 +7778,7 @@
         <v>4.4</v>
       </c>
       <c r="J141" t="n">
-        <v>1046</v>
+        <v>1056</v>
       </c>
       <c r="K141" t="n">
         <v>3.972</v>
@@ -7790,7 +7790,7 @@
         <v>4.088</v>
       </c>
       <c r="N141" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Belmont)</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -7830,7 +7830,7 @@
         <v>4.5</v>
       </c>
       <c r="J142" t="n">
-        <v>1561</v>
+        <v>1579</v>
       </c>
       <c r="K142" t="n">
         <v>4.064</v>
@@ -7842,7 +7842,7 @@
         <v>4.183</v>
       </c>
       <c r="N142" t="n">
-        <v>47.1</v>
+        <v>48.4</v>
       </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Belmont)</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -7879,22 +7879,22 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J143" t="n">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="K143" t="n">
-        <v>3.945</v>
+        <v>3.982</v>
       </c>
       <c r="L143" t="n">
-        <v>22.9</v>
+        <v>31.4</v>
       </c>
       <c r="M143" t="n">
-        <v>4.324</v>
+        <v>4.364</v>
       </c>
       <c r="N143" t="n">
-        <v>66.7</v>
+        <v>67.3</v>
       </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Belmont)</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -7934,19 +7934,19 @@
         <v>4.4</v>
       </c>
       <c r="J144" t="n">
-        <v>1959</v>
+        <v>1993</v>
       </c>
       <c r="K144" t="n">
         <v>4.005</v>
       </c>
       <c r="L144" t="n">
-        <v>39.2</v>
+        <v>35.9</v>
       </c>
       <c r="M144" t="n">
         <v>4.389</v>
       </c>
       <c r="N144" t="n">
-        <v>72.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Belmont)</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -7986,13 +7986,13 @@
         <v>4.6</v>
       </c>
       <c r="J145" t="n">
-        <v>1606</v>
+        <v>1614</v>
       </c>
       <c r="K145" t="n">
         <v>4.42</v>
       </c>
       <c r="L145" t="n">
-        <v>97.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="M145" t="n">
         <v>4.844</v>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Belmont)</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -8038,7 +8038,7 @@
         <v>4.3</v>
       </c>
       <c r="J146" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="K146" t="n">
         <v>3.884</v>
@@ -8050,7 +8050,7 @@
         <v>3.997</v>
       </c>
       <c r="N146" t="n">
-        <v>18.3</v>
+        <v>20.3</v>
       </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Belmont)</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -8090,19 +8090,19 @@
         <v>4.6</v>
       </c>
       <c r="J147" t="n">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="K147" t="n">
-        <v>4.033</v>
+        <v>4.034</v>
       </c>
       <c r="L147" t="n">
-        <v>47.1</v>
+        <v>44.4</v>
       </c>
       <c r="M147" t="n">
-        <v>4.42</v>
+        <v>4.421</v>
       </c>
       <c r="N147" t="n">
-        <v>76.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Belmont)</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -8142,7 +8142,7 @@
         <v>4.4</v>
       </c>
       <c r="J148" t="n">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="K148" t="n">
         <v>3.883</v>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Morris Park)</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -8194,19 +8194,19 @@
         <v>4.3</v>
       </c>
       <c r="J149" t="n">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="K149" t="n">
-        <v>3.93</v>
+        <v>3.931</v>
       </c>
       <c r="L149" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="M149" t="n">
-        <v>4.045</v>
+        <v>4.046</v>
       </c>
       <c r="N149" t="n">
-        <v>22.9</v>
+        <v>26.1</v>
       </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Morris Park)</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -8246,7 +8246,7 @@
         <v>4.2</v>
       </c>
       <c r="J150" t="n">
-        <v>1327</v>
+        <v>1338</v>
       </c>
       <c r="K150" t="n">
         <v>3.867</v>
@@ -8258,7 +8258,7 @@
         <v>4.238</v>
       </c>
       <c r="N150" t="n">
-        <v>52.9</v>
+        <v>53.6</v>
       </c>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Morris Park)</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -8298,19 +8298,19 @@
         <v>4.5</v>
       </c>
       <c r="J151" t="n">
-        <v>4784</v>
+        <v>4821</v>
       </c>
       <c r="K151" t="n">
         <v>4.071</v>
       </c>
       <c r="L151" t="n">
-        <v>56.2</v>
+        <v>57.5</v>
       </c>
       <c r="M151" t="n">
         <v>4.19</v>
       </c>
       <c r="N151" t="n">
-        <v>47.7</v>
+        <v>49</v>
       </c>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Throgs Neck-Schuylerville)</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -8350,13 +8350,13 @@
         <v>4.6</v>
       </c>
       <c r="J152" t="n">
-        <v>1821</v>
+        <v>1841</v>
       </c>
       <c r="K152" t="n">
         <v>4.343</v>
       </c>
       <c r="L152" t="n">
-        <v>94.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="M152" t="n">
         <v>5.155</v>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Pelham Bay-Country Club-City Island)</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -8402,13 +8402,13 @@
         <v>4.3</v>
       </c>
       <c r="J153" t="n">
-        <v>10743</v>
+        <v>10846</v>
       </c>
       <c r="K153" t="n">
         <v>3.715</v>
       </c>
       <c r="L153" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="M153" t="n">
         <v>3.619</v>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Riverdale-Spuyten Duyvil)</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -8454,19 +8454,19 @@
         <v>4.5</v>
       </c>
       <c r="J154" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K154" t="n">
         <v>3.934</v>
       </c>
       <c r="L154" t="n">
-        <v>20.9</v>
+        <v>21.6</v>
       </c>
       <c r="M154" t="n">
-        <v>4.311</v>
+        <v>4.312</v>
       </c>
       <c r="N154" t="n">
-        <v>65.40000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Bronx (Pelham Gardens)</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -8503,22 +8503,22 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J155" t="n">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="K155" t="n">
-        <v>3.98</v>
+        <v>3.935</v>
       </c>
       <c r="L155" t="n">
-        <v>30.7</v>
+        <v>22.2</v>
       </c>
       <c r="M155" t="n">
-        <v>4.362</v>
+        <v>4.312</v>
       </c>
       <c r="N155" t="n">
-        <v>69.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
